--- a/Emisiones/3.0 HV-HOJAS DE DATOS/P2437-HV-DTS-003.xlsx
+++ b/Emisiones/3.0 HV-HOJAS DE DATOS/P2437-HV-DTS-003.xlsx
@@ -22,7 +22,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.00000000000000"/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="30">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -135,35 +135,23 @@
     <font>
       <name val="Times New Roman"/>
       <b val="1"/>
-      <color rgb="001F4E78"/>
-      <sz val="14"/>
+      <color rgb="00375623"/>
+      <sz val="28"/>
     </font>
     <font>
       <name val="Times New Roman"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Times New Roman"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Times New Roman"/>
-      <b val="1"/>
-      <color rgb="001F4E78"/>
-      <sz val="12"/>
+      <sz val="28"/>
     </font>
     <font>
       <name val="Times New Roman"/>
       <i val="1"/>
       <color rgb="00404040"/>
-      <sz val="10"/>
+      <sz val="28"/>
     </font>
     <font>
       <name val="Times New Roman"/>
       <b val="1"/>
-      <sz val="11"/>
+      <sz val="28"/>
     </font>
     <font>
       <name val="Times New Roman"/>
@@ -243,8 +231,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
-        <bgColor rgb="001F4E78"/>
+        <fgColor rgb="00C6E0B4"/>
+        <bgColor rgb="00C6E0B4"/>
       </patternFill>
     </fill>
   </fills>
@@ -401,7 +389,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
@@ -519,12 +507,12 @@
     <xf numFmtId="164" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -537,74 +525,71 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="1" hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="31" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="4"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3721,89 +3706,64 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O90"/>
+  <dimension ref="A1:O67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30.6" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="6" customWidth="1" min="5" max="5"/>
-    <col width="6" customWidth="1" min="6" max="6"/>
-    <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="49" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
     <col width="13" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="13" customWidth="1" min="20" max="20"/>
     <col width="13" customWidth="1" min="21" max="21"/>
-    <col width="13" customWidth="1" min="22" max="22"/>
     <col width="13" customWidth="1" min="23" max="23"/>
     <col width="13" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
     <col width="13" customWidth="1" min="26" max="26"/>
     <col width="13" customWidth="1" min="27" max="27"/>
     <col width="13" customWidth="1" min="28" max="28"/>
     <col width="13" customWidth="1" min="29" max="29"/>
     <col width="13" customWidth="1" min="30" max="30"/>
-    <col width="13" customWidth="1" min="31" max="31"/>
     <col width="13" customWidth="1" min="32" max="32"/>
     <col width="13" customWidth="1" min="33" max="33"/>
-    <col width="13" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
-    <col width="13" customWidth="1" min="36" max="36"/>
+    <col width="13" customWidth="1" min="37" max="37"/>
     <col width="13" customWidth="1" min="38" max="38"/>
     <col width="13" customWidth="1" min="39" max="39"/>
     <col width="13" customWidth="1" min="40" max="40"/>
     <col width="13" customWidth="1" min="41" max="41"/>
     <col width="13" customWidth="1" min="42" max="42"/>
+    <col width="13" customWidth="1" min="43" max="43"/>
     <col width="13" customWidth="1" min="44" max="44"/>
+    <col width="13" customWidth="1" min="45" max="45"/>
     <col width="13" customWidth="1" min="46" max="46"/>
-    <col width="13" customWidth="1" min="47" max="47"/>
-    <col width="13" customWidth="1" min="48" max="48"/>
-    <col width="13" customWidth="1" min="49" max="49"/>
     <col width="13" customWidth="1" min="50" max="50"/>
-    <col width="13" customWidth="1" min="51" max="51"/>
     <col width="13" customWidth="1" min="52" max="52"/>
     <col width="13" customWidth="1" min="53" max="53"/>
     <col width="13" customWidth="1" min="54" max="54"/>
     <col width="13" customWidth="1" min="55" max="55"/>
+    <col width="13" customWidth="1" min="56" max="56"/>
     <col width="13" customWidth="1" min="57" max="57"/>
-    <col width="13" customWidth="1" min="58" max="58"/>
     <col width="13" customWidth="1" min="59" max="59"/>
     <col width="13" customWidth="1" min="60" max="60"/>
-    <col width="13" customWidth="1" min="62" max="62"/>
-    <col width="13" customWidth="1" min="64" max="64"/>
+    <col width="13" customWidth="1" min="61" max="61"/>
     <col width="13" customWidth="1" min="65" max="65"/>
     <col width="13" customWidth="1" min="66" max="66"/>
     <col width="13" customWidth="1" min="67" max="67"/>
-    <col width="13" customWidth="1" min="68" max="68"/>
-    <col width="13" customWidth="1" min="69" max="69"/>
-    <col width="13" customWidth="1" min="72" max="72"/>
-    <col width="13" customWidth="1" min="73" max="73"/>
-    <col width="13" customWidth="1" min="74" max="74"/>
-    <col width="13" customWidth="1" min="75" max="75"/>
-    <col width="13" customWidth="1" min="76" max="76"/>
-    <col width="13" customWidth="1" min="77" max="77"/>
-    <col width="13" customWidth="1" min="78" max="78"/>
-    <col width="13" customWidth="1" min="79" max="79"/>
-    <col width="13" customWidth="1" min="80" max="80"/>
-    <col width="13" customWidth="1" min="81" max="81"/>
-    <col width="13" customWidth="1" min="82" max="82"/>
-    <col width="13" customWidth="1" min="84" max="84"/>
-    <col width="13" customWidth="1" min="85" max="85"/>
-    <col width="13" customWidth="1" min="86" max="86"/>
-    <col width="13" customWidth="1" min="87" max="87"/>
-    <col width="13" customWidth="1" min="88" max="88"/>
-    <col width="13" customWidth="1" min="89" max="89"/>
-    <col width="13" customWidth="1" min="90" max="90"/>
   </cols>
   <sheetData>
     <row r="1" ht="29.25" customHeight="1">
@@ -4013,14 +3973,14 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" ht="345" customHeight="1">
+    <row r="9" ht="228" customHeight="1">
       <c r="A9" s="81" t="inlineStr">
         <is>
           <t>Hoja de datos: rejillas de descarga con malla anti-insectos</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
+    <row r="10" ht="38" customHeight="1">
       <c r="A10" s="82" t="inlineStr">
         <is>
           <t>Campo</t>
@@ -4045,7 +4005,7 @@
       <c r="N10" s="82" t="n"/>
       <c r="O10" s="82" t="n"/>
     </row>
-    <row r="11" ht="45" customHeight="1">
+    <row r="11" ht="38" customHeight="1">
       <c r="A11" s="83" t="inlineStr">
         <is>
           <t>Código</t>
@@ -4070,7 +4030,7 @@
       <c r="N11" s="84" t="n"/>
       <c r="O11" s="84" t="n"/>
     </row>
-    <row r="12" ht="45" customHeight="1">
+    <row r="12" ht="38" customHeight="1">
       <c r="A12" s="83" t="inlineStr">
         <is>
           <t>Revisión</t>
@@ -4095,7 +4055,7 @@
       <c r="N12" s="84" t="n"/>
       <c r="O12" s="84" t="n"/>
     </row>
-    <row r="13" ht="45" customHeight="1">
+    <row r="13" ht="38" customHeight="1">
       <c r="A13" s="83" t="inlineStr">
         <is>
           <t>Fecha</t>
@@ -4120,7 +4080,7 @@
       <c r="N13" s="84" t="n"/>
       <c r="O13" s="84" t="n"/>
     </row>
-    <row r="14" ht="240" customHeight="1">
+    <row r="14" ht="152" customHeight="1">
       <c r="A14" s="83" t="inlineStr">
         <is>
           <t>Proyecto</t>
@@ -4145,7 +4105,7 @@
       <c r="N14" s="84" t="n"/>
       <c r="O14" s="84" t="n"/>
     </row>
-    <row r="15" ht="150" customHeight="1">
+    <row r="15" ht="114" customHeight="1">
       <c r="A15" s="83" t="inlineStr">
         <is>
           <t>Etiqueta de equipo</t>
@@ -4170,72 +4130,216 @@
       <c r="N15" s="84" t="n"/>
       <c r="O15" s="84" t="n"/>
     </row>
-    <row r="16" ht="15" customHeight="1"/>
-    <row r="17" ht="15" customHeight="1"/>
-    <row r="18" ht="30" customHeight="1">
+    <row r="16" ht="38" customHeight="1"/>
+    <row r="17" ht="38" customHeight="1">
+      <c r="A17" s="81" t="inlineStr">
+        <is>
+          <t>1. Servicio</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="494" customHeight="1">
       <c r="A18" s="85" t="inlineStr">
         <is>
-          <t>1. Servicio</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="165" customHeight="1">
-      <c r="A19" s="86" t="inlineStr">
-        <is>
           <t>1.1. Descarga libre a la atmósfera del caudal de ventilación del laboratorio, a través de la envolvente del recinto. Las rejillas son la trayectoria de salida permanente del aire y, con el sistema detenido, una vía potencial de ingreso: por ello incorporan malla anti-insectos. Ambiente exterior corrosivo (atmósfera clorada de planta de hipoclorito de calcio).</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1"/>
-    <row r="21" ht="15" customHeight="1"/>
-    <row r="22" ht="15" customHeight="1"/>
-    <row r="23" ht="15" customHeight="1"/>
-    <row r="24" ht="15" customHeight="1"/>
-    <row r="25" ht="15" customHeight="1"/>
-    <row r="26" ht="105" customHeight="1">
-      <c r="A26" s="85" t="inlineStr">
+    <row r="19" ht="38" customHeight="1"/>
+    <row r="20" ht="38" customHeight="1"/>
+    <row r="21" ht="114" customHeight="1">
+      <c r="A21" s="81" t="inlineStr">
         <is>
           <t>2. Condiciones de operación y desempeño</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="105" customHeight="1">
-      <c r="A27" s="87" t="inlineStr">
+    <row r="22" ht="76" customHeight="1">
+      <c r="A22" s="86" t="inlineStr">
         <is>
           <t>Tabla 1. Condiciones de diseño (valores congelados de la memoria de cálculo).</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1"/>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="82" t="inlineStr">
+    <row r="23" ht="38" customHeight="1">
+      <c r="A23" s="82" t="inlineStr">
         <is>
           <t>Parámetro</t>
         </is>
       </c>
-      <c r="B29" s="82" t="n"/>
-      <c r="C29" s="82" t="n"/>
-      <c r="D29" s="82" t="n"/>
-      <c r="E29" s="82" t="n"/>
-      <c r="F29" s="82" t="n"/>
-      <c r="G29" s="82" t="n"/>
-      <c r="H29" s="82" t="n"/>
-      <c r="I29" s="82" t="inlineStr">
+      <c r="B23" s="82" t="n"/>
+      <c r="C23" s="82" t="n"/>
+      <c r="D23" s="82" t="n"/>
+      <c r="E23" s="82" t="n"/>
+      <c r="F23" s="82" t="n"/>
+      <c r="G23" s="82" t="n"/>
+      <c r="H23" s="82" t="n"/>
+      <c r="I23" s="82" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
       </c>
-      <c r="J29" s="82" t="n"/>
-      <c r="K29" s="82" t="n"/>
-      <c r="L29" s="82" t="n"/>
-      <c r="M29" s="82" t="n"/>
-      <c r="N29" s="82" t="n"/>
-      <c r="O29" s="82" t="n"/>
-    </row>
-    <row r="30" ht="30" customHeight="1">
+      <c r="J23" s="82" t="n"/>
+      <c r="K23" s="82" t="n"/>
+      <c r="L23" s="82" t="n"/>
+      <c r="M23" s="82" t="n"/>
+      <c r="N23" s="82" t="n"/>
+      <c r="O23" s="82" t="n"/>
+    </row>
+    <row r="24" ht="38" customHeight="1">
+      <c r="A24" s="83" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="B24" s="84" t="n"/>
+      <c r="C24" s="84" t="n"/>
+      <c r="D24" s="84" t="n"/>
+      <c r="E24" s="84" t="n"/>
+      <c r="F24" s="84" t="n"/>
+      <c r="G24" s="84" t="n"/>
+      <c r="H24" s="84" t="n"/>
+      <c r="I24" s="83" t="inlineStr">
+        <is>
+          <t>3 unidades</t>
+        </is>
+      </c>
+      <c r="J24" s="84" t="n"/>
+      <c r="K24" s="84" t="n"/>
+      <c r="L24" s="84" t="n"/>
+      <c r="M24" s="84" t="n"/>
+      <c r="N24" s="84" t="n"/>
+      <c r="O24" s="84" t="n"/>
+    </row>
+    <row r="25" ht="114" customHeight="1">
+      <c r="A25" s="83" t="inlineStr">
+        <is>
+          <t>Dimensiones faciales (unitarias)</t>
+        </is>
+      </c>
+      <c r="B25" s="84" t="n"/>
+      <c r="C25" s="84" t="n"/>
+      <c r="D25" s="84" t="n"/>
+      <c r="E25" s="84" t="n"/>
+      <c r="F25" s="84" t="n"/>
+      <c r="G25" s="84" t="n"/>
+      <c r="H25" s="84" t="n"/>
+      <c r="I25" s="83" t="inlineStr">
+        <is>
+          <t>353×336 mm (área facial 0.1187 m²)</t>
+        </is>
+      </c>
+      <c r="J25" s="84" t="n"/>
+      <c r="K25" s="84" t="n"/>
+      <c r="L25" s="84" t="n"/>
+      <c r="M25" s="84" t="n"/>
+      <c r="N25" s="84" t="n"/>
+      <c r="O25" s="84" t="n"/>
+    </row>
+    <row r="26" ht="76" customHeight="1">
+      <c r="A26" s="83" t="inlineStr">
+        <is>
+          <t>Caudal total de descarga</t>
+        </is>
+      </c>
+      <c r="B26" s="84" t="n"/>
+      <c r="C26" s="84" t="n"/>
+      <c r="D26" s="84" t="n"/>
+      <c r="E26" s="84" t="n"/>
+      <c r="F26" s="84" t="n"/>
+      <c r="G26" s="84" t="n"/>
+      <c r="H26" s="84" t="n"/>
+      <c r="I26" s="83" t="inlineStr">
+        <is>
+          <t>3 840 m³/h (1.0667 m³/s)</t>
+        </is>
+      </c>
+      <c r="J26" s="84" t="n"/>
+      <c r="K26" s="84" t="n"/>
+      <c r="L26" s="84" t="n"/>
+      <c r="M26" s="84" t="n"/>
+      <c r="N26" s="84" t="n"/>
+      <c r="O26" s="84" t="n"/>
+    </row>
+    <row r="27" ht="76" customHeight="1">
+      <c r="A27" s="83" t="inlineStr">
+        <is>
+          <t>Velocidad facial</t>
+        </is>
+      </c>
+      <c r="B27" s="84" t="n"/>
+      <c r="C27" s="84" t="n"/>
+      <c r="D27" s="84" t="n"/>
+      <c r="E27" s="84" t="n"/>
+      <c r="F27" s="84" t="n"/>
+      <c r="G27" s="84" t="n"/>
+      <c r="H27" s="84" t="n"/>
+      <c r="I27" s="83" t="inlineStr">
+        <is>
+          <t>3 m/s</t>
+        </is>
+      </c>
+      <c r="J27" s="84" t="n"/>
+      <c r="K27" s="84" t="n"/>
+      <c r="L27" s="84" t="n"/>
+      <c r="M27" s="84" t="n"/>
+      <c r="N27" s="84" t="n"/>
+      <c r="O27" s="84" t="n"/>
+    </row>
+    <row r="28" ht="152" customHeight="1">
+      <c r="A28" s="83" t="inlineStr">
+        <is>
+          <t>ΔP unitaria (cierre de orificio, C_d = 0.60, en el sitio)</t>
+        </is>
+      </c>
+      <c r="B28" s="84" t="n"/>
+      <c r="C28" s="84" t="n"/>
+      <c r="D28" s="84" t="n"/>
+      <c r="E28" s="84" t="n"/>
+      <c r="F28" s="84" t="n"/>
+      <c r="G28" s="84" t="n"/>
+      <c r="H28" s="84" t="n"/>
+      <c r="I28" s="83" t="inlineStr">
+        <is>
+          <t>11 Pa</t>
+        </is>
+      </c>
+      <c r="J28" s="84" t="n"/>
+      <c r="K28" s="84" t="n"/>
+      <c r="L28" s="84" t="n"/>
+      <c r="M28" s="84" t="n"/>
+      <c r="N28" s="84" t="n"/>
+      <c r="O28" s="84" t="n"/>
+    </row>
+    <row r="29" ht="152" customHeight="1">
+      <c r="A29" s="83" t="inlineStr">
+        <is>
+          <t>ΔP equivalente a densidad estándar (ρ = 1.2 kg/m³)</t>
+        </is>
+      </c>
+      <c r="B29" s="84" t="n"/>
+      <c r="C29" s="84" t="n"/>
+      <c r="D29" s="84" t="n"/>
+      <c r="E29" s="84" t="n"/>
+      <c r="F29" s="84" t="n"/>
+      <c r="G29" s="84" t="n"/>
+      <c r="H29" s="84" t="n"/>
+      <c r="I29" s="83" t="inlineStr">
+        <is>
+          <t>15 Pa</t>
+        </is>
+      </c>
+      <c r="J29" s="84" t="n"/>
+      <c r="K29" s="84" t="n"/>
+      <c r="L29" s="84" t="n"/>
+      <c r="M29" s="84" t="n"/>
+      <c r="N29" s="84" t="n"/>
+      <c r="O29" s="84" t="n"/>
+    </row>
+    <row r="30" ht="114" customHeight="1">
       <c r="A30" s="83" t="inlineStr">
         <is>
-          <t>Cantidad</t>
+          <t>Densidad del aire de diseño</t>
         </is>
       </c>
       <c r="B30" s="84" t="n"/>
@@ -4247,7 +4351,7 @@
       <c r="H30" s="84" t="n"/>
       <c r="I30" s="83" t="inlineStr">
         <is>
-          <t>3 unidades</t>
+          <t>0.88 kg/m³ (2 558 msnm, 74.1 kPa)</t>
         </is>
       </c>
       <c r="J30" s="84" t="n"/>
@@ -4257,846 +4361,676 @@
       <c r="N30" s="84" t="n"/>
       <c r="O30" s="84" t="n"/>
     </row>
-    <row r="31" ht="105" customHeight="1">
-      <c r="A31" s="83" t="inlineStr">
-        <is>
-          <t>Dimensiones faciales (unitarias)</t>
-        </is>
-      </c>
-      <c r="B31" s="84" t="n"/>
-      <c r="C31" s="84" t="n"/>
-      <c r="D31" s="84" t="n"/>
-      <c r="E31" s="84" t="n"/>
-      <c r="F31" s="84" t="n"/>
-      <c r="G31" s="84" t="n"/>
-      <c r="H31" s="84" t="n"/>
-      <c r="I31" s="83" t="inlineStr">
-        <is>
-          <t>353×336 mm (área facial 0.1187 m²)</t>
-        </is>
-      </c>
-      <c r="J31" s="84" t="n"/>
-      <c r="K31" s="84" t="n"/>
-      <c r="L31" s="84" t="n"/>
-      <c r="M31" s="84" t="n"/>
-      <c r="N31" s="84" t="n"/>
-      <c r="O31" s="84" t="n"/>
-    </row>
-    <row r="32" ht="75" customHeight="1">
-      <c r="A32" s="83" t="inlineStr">
-        <is>
-          <t>Caudal total de descarga</t>
-        </is>
-      </c>
-      <c r="B32" s="84" t="n"/>
-      <c r="C32" s="84" t="n"/>
-      <c r="D32" s="84" t="n"/>
-      <c r="E32" s="84" t="n"/>
-      <c r="F32" s="84" t="n"/>
-      <c r="G32" s="84" t="n"/>
-      <c r="H32" s="84" t="n"/>
-      <c r="I32" s="83" t="inlineStr">
-        <is>
-          <t>3 840 m³/h (1.0667 m³/s)</t>
-        </is>
-      </c>
-      <c r="J32" s="84" t="n"/>
-      <c r="K32" s="84" t="n"/>
-      <c r="L32" s="84" t="n"/>
-      <c r="M32" s="84" t="n"/>
-      <c r="N32" s="84" t="n"/>
-      <c r="O32" s="84" t="n"/>
-    </row>
-    <row r="33" ht="45" customHeight="1">
-      <c r="A33" s="83" t="inlineStr">
-        <is>
-          <t>Velocidad facial</t>
-        </is>
-      </c>
-      <c r="B33" s="84" t="n"/>
-      <c r="C33" s="84" t="n"/>
-      <c r="D33" s="84" t="n"/>
-      <c r="E33" s="84" t="n"/>
-      <c r="F33" s="84" t="n"/>
-      <c r="G33" s="84" t="n"/>
-      <c r="H33" s="84" t="n"/>
-      <c r="I33" s="83" t="inlineStr">
-        <is>
-          <t>3 m/s</t>
-        </is>
-      </c>
-      <c r="J33" s="84" t="n"/>
-      <c r="K33" s="84" t="n"/>
-      <c r="L33" s="84" t="n"/>
-      <c r="M33" s="84" t="n"/>
-      <c r="N33" s="84" t="n"/>
-      <c r="O33" s="84" t="n"/>
-    </row>
-    <row r="34" ht="165" customHeight="1">
-      <c r="A34" s="83" t="inlineStr">
-        <is>
-          <t>ΔP unitaria (cierre de orificio, C_d = 0.60, en el sitio)</t>
-        </is>
-      </c>
-      <c r="B34" s="84" t="n"/>
-      <c r="C34" s="84" t="n"/>
-      <c r="D34" s="84" t="n"/>
-      <c r="E34" s="84" t="n"/>
-      <c r="F34" s="84" t="n"/>
-      <c r="G34" s="84" t="n"/>
-      <c r="H34" s="84" t="n"/>
-      <c r="I34" s="83" t="inlineStr">
-        <is>
-          <t>11 Pa</t>
-        </is>
-      </c>
-      <c r="J34" s="84" t="n"/>
-      <c r="K34" s="84" t="n"/>
-      <c r="L34" s="84" t="n"/>
-      <c r="M34" s="84" t="n"/>
-      <c r="N34" s="84" t="n"/>
-      <c r="O34" s="84" t="n"/>
-    </row>
-    <row r="35" ht="135" customHeight="1">
-      <c r="A35" s="83" t="inlineStr">
-        <is>
-          <t>ΔP equivalente a densidad estándar (ρ = 1.2 kg/m³)</t>
-        </is>
-      </c>
-      <c r="B35" s="84" t="n"/>
-      <c r="C35" s="84" t="n"/>
-      <c r="D35" s="84" t="n"/>
-      <c r="E35" s="84" t="n"/>
-      <c r="F35" s="84" t="n"/>
-      <c r="G35" s="84" t="n"/>
-      <c r="H35" s="84" t="n"/>
-      <c r="I35" s="83" t="inlineStr">
-        <is>
-          <t>15 Pa</t>
-        </is>
-      </c>
-      <c r="J35" s="84" t="n"/>
-      <c r="K35" s="84" t="n"/>
-      <c r="L35" s="84" t="n"/>
-      <c r="M35" s="84" t="n"/>
-      <c r="N35" s="84" t="n"/>
-      <c r="O35" s="84" t="n"/>
-    </row>
-    <row r="36" ht="90" customHeight="1">
-      <c r="A36" s="83" t="inlineStr">
-        <is>
-          <t>Densidad del aire de diseño</t>
-        </is>
-      </c>
-      <c r="B36" s="84" t="n"/>
-      <c r="C36" s="84" t="n"/>
-      <c r="D36" s="84" t="n"/>
-      <c r="E36" s="84" t="n"/>
-      <c r="F36" s="84" t="n"/>
-      <c r="G36" s="84" t="n"/>
-      <c r="H36" s="84" t="n"/>
-      <c r="I36" s="83" t="inlineStr">
-        <is>
-          <t>0.88 kg/m³ (2 558 msnm, 74.1 kPa)</t>
-        </is>
-      </c>
-      <c r="J36" s="84" t="n"/>
-      <c r="K36" s="84" t="n"/>
-      <c r="L36" s="84" t="n"/>
-      <c r="M36" s="84" t="n"/>
-      <c r="N36" s="84" t="n"/>
-      <c r="O36" s="84" t="n"/>
-    </row>
-    <row r="37" ht="15" customHeight="1"/>
-    <row r="38" ht="165" customHeight="1">
-      <c r="A38" s="86" t="inlineStr">
+    <row r="31" ht="38" customHeight="1"/>
+    <row r="32" ht="418" customHeight="1">
+      <c r="A32" s="85" t="inlineStr">
         <is>
           <t>2.1. Nota de contexto: la ΔP unitaria de 11 Pa (cierre de orificio, C_d = 0.60, a 3 m/s) es la pérdida de descarga libre a la atmósfera y se suma a la caída de presión de la etapa filtrante para definir el punto de trabajo del ventilador; no existe consigna de presión interior que sostener.</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="15" customHeight="1"/>
-    <row r="40" ht="15" customHeight="1"/>
-    <row r="41" ht="15" customHeight="1"/>
-    <row r="42" ht="15" customHeight="1"/>
-    <row r="43" ht="15" customHeight="1"/>
-    <row r="44" ht="90" customHeight="1">
-      <c r="A44" s="85" t="inlineStr">
+    <row r="33" ht="38" customHeight="1"/>
+    <row r="34" ht="38" customHeight="1"/>
+    <row r="35" ht="114" customHeight="1">
+      <c r="A35" s="81" t="inlineStr">
         <is>
           <t>3. Construcción y áreas netas</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="45" customHeight="1">
-      <c r="A45" s="87" t="inlineStr">
+    <row r="36" ht="38" customHeight="1">
+      <c r="A36" s="86" t="inlineStr">
         <is>
           <t>Tabla 2. Especificación constructiva.</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="45" customHeight="1">
-      <c r="A46" s="82" t="inlineStr">
+    <row r="37" ht="38" customHeight="1">
+      <c r="A37" s="82" t="inlineStr">
         <is>
           <t>Característica</t>
         </is>
       </c>
-      <c r="B46" s="82" t="n"/>
-      <c r="C46" s="82" t="n"/>
-      <c r="D46" s="82" t="n"/>
-      <c r="E46" s="82" t="n"/>
-      <c r="F46" s="82" t="n"/>
-      <c r="G46" s="82" t="n"/>
-      <c r="H46" s="82" t="n"/>
-      <c r="I46" s="82" t="inlineStr">
+      <c r="B37" s="82" t="n"/>
+      <c r="C37" s="82" t="n"/>
+      <c r="D37" s="82" t="n"/>
+      <c r="E37" s="82" t="n"/>
+      <c r="F37" s="82" t="n"/>
+      <c r="G37" s="82" t="n"/>
+      <c r="H37" s="82" t="n"/>
+      <c r="I37" s="82" t="inlineStr">
         <is>
           <t>Especificación</t>
         </is>
       </c>
-      <c r="J46" s="82" t="n"/>
-      <c r="K46" s="82" t="n"/>
-      <c r="L46" s="82" t="n"/>
-      <c r="M46" s="82" t="n"/>
-      <c r="N46" s="82" t="n"/>
-      <c r="O46" s="82" t="n"/>
-    </row>
-    <row r="47" ht="150" customHeight="1">
-      <c r="A47" s="83" t="inlineStr">
+      <c r="J37" s="82" t="n"/>
+      <c r="K37" s="82" t="n"/>
+      <c r="L37" s="82" t="n"/>
+      <c r="M37" s="82" t="n"/>
+      <c r="N37" s="82" t="n"/>
+      <c r="O37" s="82" t="n"/>
+    </row>
+    <row r="38" ht="152" customHeight="1">
+      <c r="A38" s="83" t="inlineStr">
         <is>
           <t>Tipo de núcleo</t>
         </is>
       </c>
-      <c r="B47" s="84" t="n"/>
-      <c r="C47" s="84" t="n"/>
-      <c r="D47" s="84" t="n"/>
-      <c r="E47" s="84" t="n"/>
-      <c r="F47" s="84" t="n"/>
-      <c r="G47" s="84" t="n"/>
-      <c r="H47" s="84" t="n"/>
-      <c r="I47" s="83" t="inlineStr">
+      <c r="B38" s="84" t="n"/>
+      <c r="C38" s="84" t="n"/>
+      <c r="D38" s="84" t="n"/>
+      <c r="E38" s="84" t="n"/>
+      <c r="F38" s="84" t="n"/>
+      <c r="G38" s="84" t="n"/>
+      <c r="H38" s="84" t="n"/>
+      <c r="I38" s="83" t="inlineStr">
         <is>
           <t>Eggcrate (panal) ½×½×½ in (12.7 mm), máxima área libre</t>
         </is>
       </c>
-      <c r="J47" s="84" t="n"/>
-      <c r="K47" s="84" t="n"/>
-      <c r="L47" s="84" t="n"/>
-      <c r="M47" s="84" t="n"/>
-      <c r="N47" s="84" t="n"/>
-      <c r="O47" s="84" t="n"/>
-    </row>
-    <row r="48" ht="450" customHeight="1">
-      <c r="A48" s="83" t="inlineStr">
+      <c r="J38" s="84" t="n"/>
+      <c r="K38" s="84" t="n"/>
+      <c r="L38" s="84" t="n"/>
+      <c r="M38" s="84" t="n"/>
+      <c r="N38" s="84" t="n"/>
+      <c r="O38" s="84" t="n"/>
+    </row>
+    <row r="39" ht="456" customHeight="1">
+      <c r="A39" s="83" t="inlineStr">
         <is>
           <t>Área libre del núcleo</t>
         </is>
       </c>
-      <c r="B48" s="84" t="n"/>
-      <c r="C48" s="84" t="n"/>
-      <c r="D48" s="84" t="n"/>
-      <c r="E48" s="84" t="n"/>
-      <c r="F48" s="84" t="n"/>
-      <c r="G48" s="84" t="n"/>
-      <c r="H48" s="84" t="n"/>
-      <c r="I48" s="83" t="inlineStr">
+      <c r="B39" s="84" t="n"/>
+      <c r="C39" s="84" t="n"/>
+      <c r="D39" s="84" t="n"/>
+      <c r="E39" s="84" t="n"/>
+      <c r="F39" s="84" t="n"/>
+      <c r="G39" s="84" t="n"/>
+      <c r="H39" s="84" t="n"/>
+      <c r="I39" s="83" t="inlineStr">
         <is>
           <t>≥ 90 % (cifra repetida en catálogos del tipo; Airfoil RC-FCR5 (https://airfoil.com.au/product/removable-core-fixing-clip-eggcrate-grille-rc-fcr5/), consulta 2026-07-23)</t>
         </is>
       </c>
-      <c r="J48" s="84" t="n"/>
-      <c r="K48" s="84" t="n"/>
-      <c r="L48" s="84" t="n"/>
-      <c r="M48" s="84" t="n"/>
-      <c r="N48" s="84" t="n"/>
-      <c r="O48" s="84" t="n"/>
-    </row>
-    <row r="49" ht="705" customHeight="1">
-      <c r="A49" s="83" t="inlineStr">
+      <c r="J39" s="84" t="n"/>
+      <c r="K39" s="84" t="n"/>
+      <c r="L39" s="84" t="n"/>
+      <c r="M39" s="84" t="n"/>
+      <c r="N39" s="84" t="n"/>
+      <c r="O39" s="84" t="n"/>
+    </row>
+    <row r="40" ht="722" customHeight="1">
+      <c r="A40" s="83" t="inlineStr">
         <is>
           <t>Malla anti-insectos</t>
         </is>
       </c>
-      <c r="B49" s="84" t="n"/>
-      <c r="C49" s="84" t="n"/>
-      <c r="D49" s="84" t="n"/>
-      <c r="E49" s="84" t="n"/>
-      <c r="F49" s="84" t="n"/>
-      <c r="G49" s="84" t="n"/>
-      <c r="H49" s="84" t="n"/>
-      <c r="I49" s="83" t="inlineStr">
+      <c r="B40" s="84" t="n"/>
+      <c r="C40" s="84" t="n"/>
+      <c r="D40" s="84" t="n"/>
+      <c r="E40" s="84" t="n"/>
+      <c r="F40" s="84" t="n"/>
+      <c r="G40" s="84" t="n"/>
+      <c r="H40" s="84" t="n"/>
+      <c r="I40" s="83" t="inlineStr">
         <is>
           <t>Tejido 18×18, abertura ≈1 mm, alambre 0.45 mm, área abierta ≥ 48 % (tabla Industrial Metal Mesh (https://www.industrialmetalmesh.com/sale-54819921-micron-304-316l-stainless-steel-wire-mesh-screen-filter-mesh.html), consulta 2026-07-23); excluye insectos comunes</t>
         </is>
       </c>
-      <c r="J49" s="84" t="n"/>
-      <c r="K49" s="84" t="n"/>
-      <c r="L49" s="84" t="n"/>
-      <c r="M49" s="84" t="n"/>
-      <c r="N49" s="84" t="n"/>
-      <c r="O49" s="84" t="n"/>
-    </row>
-    <row r="50" ht="135" customHeight="1">
-      <c r="A50" s="83" t="inlineStr">
+      <c r="J40" s="84" t="n"/>
+      <c r="K40" s="84" t="n"/>
+      <c r="L40" s="84" t="n"/>
+      <c r="M40" s="84" t="n"/>
+      <c r="N40" s="84" t="n"/>
+      <c r="O40" s="84" t="n"/>
+    </row>
+    <row r="41" ht="152" customHeight="1">
+      <c r="A41" s="83" t="inlineStr">
         <is>
           <t>Área neta combinada (núcleo + malla)</t>
         </is>
       </c>
-      <c r="B50" s="84" t="n"/>
-      <c r="C50" s="84" t="n"/>
-      <c r="D50" s="84" t="n"/>
-      <c r="E50" s="84" t="n"/>
-      <c r="F50" s="84" t="n"/>
-      <c r="G50" s="84" t="n"/>
-      <c r="H50" s="84" t="n"/>
-      <c r="I50" s="83" t="inlineStr">
+      <c r="B41" s="84" t="n"/>
+      <c r="C41" s="84" t="n"/>
+      <c r="D41" s="84" t="n"/>
+      <c r="E41" s="84" t="n"/>
+      <c r="F41" s="84" t="n"/>
+      <c r="G41" s="84" t="n"/>
+      <c r="H41" s="84" t="n"/>
+      <c r="I41" s="83" t="inlineStr">
         <is>
           <t>≈ 45 % del área facial (dato típico: 0.90 × 0.50)</t>
         </is>
       </c>
-      <c r="J50" s="84" t="n"/>
-      <c r="K50" s="84" t="n"/>
-      <c r="L50" s="84" t="n"/>
-      <c r="M50" s="84" t="n"/>
-      <c r="N50" s="84" t="n"/>
-      <c r="O50" s="84" t="n"/>
-    </row>
-    <row r="51" ht="195" customHeight="1">
-      <c r="A51" s="83" t="inlineStr">
+      <c r="J41" s="84" t="n"/>
+      <c r="K41" s="84" t="n"/>
+      <c r="L41" s="84" t="n"/>
+      <c r="M41" s="84" t="n"/>
+      <c r="N41" s="84" t="n"/>
+      <c r="O41" s="84" t="n"/>
+    </row>
+    <row r="42" ht="190" customHeight="1">
+      <c r="A42" s="83" t="inlineStr">
         <is>
           <t>Material de la rejilla</t>
         </is>
       </c>
-      <c r="B51" s="84" t="n"/>
-      <c r="C51" s="84" t="n"/>
-      <c r="D51" s="84" t="n"/>
-      <c r="E51" s="84" t="n"/>
-      <c r="F51" s="84" t="n"/>
-      <c r="G51" s="84" t="n"/>
-      <c r="H51" s="84" t="n"/>
-      <c r="I51" s="83" t="inlineStr">
+      <c r="B42" s="84" t="n"/>
+      <c r="C42" s="84" t="n"/>
+      <c r="D42" s="84" t="n"/>
+      <c r="E42" s="84" t="n"/>
+      <c r="F42" s="84" t="n"/>
+      <c r="G42" s="84" t="n"/>
+      <c r="H42" s="84" t="n"/>
+      <c r="I42" s="83" t="inlineStr">
         <is>
           <t>Inox 316L (primera opción) o aluminio anodizado 6063-T5 (alternativa)</t>
         </is>
       </c>
-      <c r="J51" s="84" t="n"/>
-      <c r="K51" s="84" t="n"/>
-      <c r="L51" s="84" t="n"/>
-      <c r="M51" s="84" t="n"/>
-      <c r="N51" s="84" t="n"/>
-      <c r="O51" s="84" t="n"/>
-    </row>
-    <row r="52" ht="60" customHeight="1">
-      <c r="A52" s="83" t="inlineStr">
+      <c r="J42" s="84" t="n"/>
+      <c r="K42" s="84" t="n"/>
+      <c r="L42" s="84" t="n"/>
+      <c r="M42" s="84" t="n"/>
+      <c r="N42" s="84" t="n"/>
+      <c r="O42" s="84" t="n"/>
+    </row>
+    <row r="43" ht="76" customHeight="1">
+      <c r="A43" s="83" t="inlineStr">
         <is>
           <t>Material de la malla</t>
         </is>
       </c>
-      <c r="B52" s="84" t="n"/>
-      <c r="C52" s="84" t="n"/>
-      <c r="D52" s="84" t="n"/>
-      <c r="E52" s="84" t="n"/>
-      <c r="F52" s="84" t="n"/>
-      <c r="G52" s="84" t="n"/>
-      <c r="H52" s="84" t="n"/>
-      <c r="I52" s="83" t="inlineStr">
+      <c r="B43" s="84" t="n"/>
+      <c r="C43" s="84" t="n"/>
+      <c r="D43" s="84" t="n"/>
+      <c r="E43" s="84" t="n"/>
+      <c r="F43" s="84" t="n"/>
+      <c r="G43" s="84" t="n"/>
+      <c r="H43" s="84" t="n"/>
+      <c r="I43" s="83" t="inlineStr">
         <is>
           <t>Inox 316</t>
         </is>
       </c>
-      <c r="J52" s="84" t="n"/>
-      <c r="K52" s="84" t="n"/>
-      <c r="L52" s="84" t="n"/>
-      <c r="M52" s="84" t="n"/>
-      <c r="N52" s="84" t="n"/>
-      <c r="O52" s="84" t="n"/>
-    </row>
-    <row r="53" ht="120" customHeight="1">
+      <c r="J43" s="84" t="n"/>
+      <c r="K43" s="84" t="n"/>
+      <c r="L43" s="84" t="n"/>
+      <c r="M43" s="84" t="n"/>
+      <c r="N43" s="84" t="n"/>
+      <c r="O43" s="84" t="n"/>
+    </row>
+    <row r="44" ht="114" customHeight="1">
+      <c r="A44" s="83" t="inlineStr">
+        <is>
+          <t>Montaje de la malla</t>
+        </is>
+      </c>
+      <c r="B44" s="84" t="n"/>
+      <c r="C44" s="84" t="n"/>
+      <c r="D44" s="84" t="n"/>
+      <c r="E44" s="84" t="n"/>
+      <c r="F44" s="84" t="n"/>
+      <c r="G44" s="84" t="n"/>
+      <c r="H44" s="84" t="n"/>
+      <c r="I44" s="83" t="inlineStr">
+        <is>
+          <t>Marco desmontable para limpieza periódica</t>
+        </is>
+      </c>
+      <c r="J44" s="84" t="n"/>
+      <c r="K44" s="84" t="n"/>
+      <c r="L44" s="84" t="n"/>
+      <c r="M44" s="84" t="n"/>
+      <c r="N44" s="84" t="n"/>
+      <c r="O44" s="84" t="n"/>
+    </row>
+    <row r="45" ht="266" customHeight="1">
+      <c r="A45" s="83" t="inlineStr">
+        <is>
+          <t>Par galvánico</t>
+        </is>
+      </c>
+      <c r="B45" s="84" t="n"/>
+      <c r="C45" s="84" t="n"/>
+      <c r="D45" s="84" t="n"/>
+      <c r="E45" s="84" t="n"/>
+      <c r="F45" s="84" t="n"/>
+      <c r="G45" s="84" t="n"/>
+      <c r="H45" s="84" t="n"/>
+      <c r="I45" s="83" t="inlineStr">
+        <is>
+          <t>Si se combina marco de aluminio con malla inox, aislamiento dieléctrico (dato típico de ingeniería)</t>
+        </is>
+      </c>
+      <c r="J45" s="84" t="n"/>
+      <c r="K45" s="84" t="n"/>
+      <c r="L45" s="84" t="n"/>
+      <c r="M45" s="84" t="n"/>
+      <c r="N45" s="84" t="n"/>
+      <c r="O45" s="84" t="n"/>
+    </row>
+    <row r="46" ht="114" customHeight="1">
+      <c r="A46" s="83" t="inlineStr">
+        <is>
+          <t>Ensayo de desempeño</t>
+        </is>
+      </c>
+      <c r="B46" s="84" t="n"/>
+      <c r="C46" s="84" t="n"/>
+      <c r="D46" s="84" t="n"/>
+      <c r="E46" s="84" t="n"/>
+      <c r="F46" s="84" t="n"/>
+      <c r="G46" s="84" t="n"/>
+      <c r="H46" s="84" t="n"/>
+      <c r="I46" s="83" t="inlineStr">
+        <is>
+          <t>ASHRAE 70 (medición de rejillas)</t>
+        </is>
+      </c>
+      <c r="J46" s="84" t="n"/>
+      <c r="K46" s="84" t="n"/>
+      <c r="L46" s="84" t="n"/>
+      <c r="M46" s="84" t="n"/>
+      <c r="N46" s="84" t="n"/>
+      <c r="O46" s="84" t="n"/>
+    </row>
+    <row r="47" ht="38" customHeight="1"/>
+    <row r="48" ht="190" customHeight="1">
+      <c r="A48" s="85" t="inlineStr">
+        <is>
+          <t>3.1. La malla domina la pérdida del conjunto; el dimensionamiento por área neta combinada y la ΔP calculada por cierre de orificio (11 Pa) deben verificarse contra el área efectiva (Ak) del fabricante seleccionado (por confirmar con proveedor).</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="38" customHeight="1"/>
+    <row r="50" ht="76" customHeight="1">
+      <c r="A50" s="81" t="inlineStr">
+        <is>
+          <t>4. Candidatos comerciales</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="38" customHeight="1">
+      <c r="A51" s="86" t="inlineStr">
+        <is>
+          <t>Tabla 3. Candidatos (consulta 2026-07-23).</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="76" customHeight="1">
+      <c r="A52" s="82" t="inlineStr">
+        <is>
+          <t>Producto</t>
+        </is>
+      </c>
+      <c r="B52" s="82" t="n"/>
+      <c r="C52" s="82" t="n"/>
+      <c r="D52" s="82" t="inlineStr">
+        <is>
+          <t>Tipo / material</t>
+        </is>
+      </c>
+      <c r="E52" s="82" t="n"/>
+      <c r="F52" s="82" t="n"/>
+      <c r="G52" s="82" t="inlineStr">
+        <is>
+          <t>Pros</t>
+        </is>
+      </c>
+      <c r="H52" s="82" t="n"/>
+      <c r="I52" s="82" t="n"/>
+      <c r="J52" s="82" t="inlineStr">
+        <is>
+          <t>Contras</t>
+        </is>
+      </c>
+      <c r="K52" s="82" t="n"/>
+      <c r="L52" s="82" t="n"/>
+      <c r="M52" s="82" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="N52" s="82" t="n"/>
+      <c r="O52" s="82" t="n"/>
+    </row>
+    <row r="53" ht="266" customHeight="1">
       <c r="A53" s="83" t="inlineStr">
         <is>
-          <t>Montaje de la malla</t>
+          <t>Titus 50F / 50R</t>
         </is>
       </c>
       <c r="B53" s="84" t="n"/>
       <c r="C53" s="84" t="n"/>
-      <c r="D53" s="84" t="n"/>
+      <c r="D53" s="83" t="inlineStr">
+        <is>
+          <t>Eggcrate ½ in; aluminio, con versión íntegramente inox de fábrica</t>
+        </is>
+      </c>
       <c r="E53" s="84" t="n"/>
       <c r="F53" s="84" t="n"/>
-      <c r="G53" s="84" t="n"/>
+      <c r="G53" s="83" t="inlineStr">
+        <is>
+          <t>«Highest free area of any return grille»; única opción inox de catálogo</t>
+        </is>
+      </c>
       <c r="H53" s="84" t="n"/>
-      <c r="I53" s="83" t="inlineStr">
-        <is>
-          <t>Marco desmontable para limpieza periódica</t>
-        </is>
-      </c>
-      <c r="J53" s="84" t="n"/>
+      <c r="I53" s="84" t="n"/>
+      <c r="J53" s="83" t="inlineStr">
+        <is>
+          <t>Importación; tamaño 353×336 por pedido</t>
+        </is>
+      </c>
       <c r="K53" s="84" t="n"/>
       <c r="L53" s="84" t="n"/>
-      <c r="M53" s="84" t="n"/>
+      <c r="M53" s="83" t="inlineStr">
+        <is>
+          <t>Titus 50F (PDF) (https://www.titus-hvac.com/file/1228/50F_50Rrprod_specialized_2017.pdf)</t>
+        </is>
+      </c>
       <c r="N53" s="84" t="n"/>
       <c r="O53" s="84" t="n"/>
     </row>
-    <row r="54" ht="270" customHeight="1">
+    <row r="54" ht="266" customHeight="1">
       <c r="A54" s="83" t="inlineStr">
         <is>
-          <t>Par galvánico</t>
+          <t>Krueger EGC5</t>
         </is>
       </c>
       <c r="B54" s="84" t="n"/>
       <c r="C54" s="84" t="n"/>
-      <c r="D54" s="84" t="n"/>
+      <c r="D54" s="83" t="inlineStr">
+        <is>
+          <t>Eggcrate ½ in; aluminio</t>
+        </is>
+      </c>
       <c r="E54" s="84" t="n"/>
       <c r="F54" s="84" t="n"/>
-      <c r="G54" s="84" t="n"/>
+      <c r="G54" s="83" t="inlineStr">
+        <is>
+          <t>Amplia gama de tamaños (6×4 in a 96×96 in)</t>
+        </is>
+      </c>
       <c r="H54" s="84" t="n"/>
-      <c r="I54" s="83" t="inlineStr">
-        <is>
-          <t>Si se combina marco de aluminio con malla inox, aislamiento dieléctrico (dato típico de ingeniería)</t>
-        </is>
-      </c>
-      <c r="J54" s="84" t="n"/>
+      <c r="I54" s="84" t="n"/>
+      <c r="J54" s="83" t="inlineStr">
+        <is>
+          <t>Sin ejecución inox</t>
+        </is>
+      </c>
       <c r="K54" s="84" t="n"/>
       <c r="L54" s="84" t="n"/>
-      <c r="M54" s="84" t="n"/>
+      <c r="M54" s="83" t="inlineStr">
+        <is>
+          <t>Krueger EGC5 (https://www.krueger-hvac.com/Catalog%20Home/Grilles/Grilles%20-%20Return/EGC5)</t>
+        </is>
+      </c>
       <c r="N54" s="84" t="n"/>
       <c r="O54" s="84" t="n"/>
     </row>
-    <row r="55" ht="90" customHeight="1">
+    <row r="55" ht="266" customHeight="1">
       <c r="A55" s="83" t="inlineStr">
         <is>
-          <t>Ensayo de desempeño</t>
+          <t>ProAire S.A.S (Bogotá)</t>
         </is>
       </c>
       <c r="B55" s="84" t="n"/>
       <c r="C55" s="84" t="n"/>
-      <c r="D55" s="84" t="n"/>
+      <c r="D55" s="83" t="inlineStr">
+        <is>
+          <t>Fabricación a medida con corte láser, inox 316</t>
+        </is>
+      </c>
       <c r="E55" s="84" t="n"/>
       <c r="F55" s="84" t="n"/>
-      <c r="G55" s="84" t="n"/>
+      <c r="G55" s="83" t="inlineStr">
+        <is>
+          <t>Medida exacta 353×336 y ejecución inox 316L local; vía recomendada</t>
+        </is>
+      </c>
       <c r="H55" s="84" t="n"/>
-      <c r="I55" s="83" t="inlineStr">
-        <is>
-          <t>ASHRAE 70 (medición de rejillas)</t>
-        </is>
-      </c>
-      <c r="J55" s="84" t="n"/>
+      <c r="I55" s="84" t="n"/>
+      <c r="J55" s="83" t="inlineStr">
+        <is>
+          <t>Submittal y Ak por confirmar con proveedor</t>
+        </is>
+      </c>
       <c r="K55" s="84" t="n"/>
       <c r="L55" s="84" t="n"/>
-      <c r="M55" s="84" t="n"/>
+      <c r="M55" s="83" t="inlineStr">
+        <is>
+          <t>proairecolombia.com (https://www.proairecolombia.com/productos/rejillas-y-difusores.html)</t>
+        </is>
+      </c>
       <c r="N55" s="84" t="n"/>
       <c r="O55" s="84" t="n"/>
     </row>
-    <row r="56" ht="15" customHeight="1"/>
-    <row r="57" ht="165" customHeight="1">
-      <c r="A57" s="86" t="inlineStr">
-        <is>
-          <t>3.1. La malla domina la pérdida del conjunto; el dimensionamiento por área neta combinada y la ΔP calculada por cierre de orificio (11 Pa) deben verificarse contra el área efectiva (Ak) del fabricante seleccionado (por confirmar con proveedor).</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="15" customHeight="1"/>
-    <row r="59" ht="15" customHeight="1"/>
-    <row r="60" ht="15" customHeight="1"/>
-    <row r="61" ht="15" customHeight="1"/>
-    <row r="62" ht="75" customHeight="1">
+    <row r="56" ht="190" customHeight="1">
+      <c r="A56" s="83" t="inlineStr">
+        <is>
+          <t>Laminaire (Colombia)</t>
+        </is>
+      </c>
+      <c r="B56" s="84" t="n"/>
+      <c r="C56" s="84" t="n"/>
+      <c r="D56" s="83" t="inlineStr">
+        <is>
+          <t>Rejillas y difusores en aluminio a pedido</t>
+        </is>
+      </c>
+      <c r="E56" s="84" t="n"/>
+      <c r="F56" s="84" t="n"/>
+      <c r="G56" s="83" t="inlineStr">
+        <is>
+          <t>Fabricación local con software de selección; marco para malla a pedido</t>
+        </is>
+      </c>
+      <c r="H56" s="84" t="n"/>
+      <c r="I56" s="84" t="n"/>
+      <c r="J56" s="83" t="inlineStr">
+        <is>
+          <t>Confirmar ejecución inox</t>
+        </is>
+      </c>
+      <c r="K56" s="84" t="n"/>
+      <c r="L56" s="84" t="n"/>
+      <c r="M56" s="83" t="inlineStr">
+        <is>
+          <t>laminaire.net (https://laminaire.net/)</t>
+        </is>
+      </c>
+      <c r="N56" s="84" t="n"/>
+      <c r="O56" s="84" t="n"/>
+    </row>
+    <row r="57" ht="114" customHeight="1">
+      <c r="A57" s="83" t="inlineStr">
+        <is>
+          <t>CL Ingeniería (Bogotá)</t>
+        </is>
+      </c>
+      <c r="B57" s="84" t="n"/>
+      <c r="C57" s="84" t="n"/>
+      <c r="D57" s="83" t="inlineStr">
+        <is>
+          <t>Rejillas y accesorios HVAC</t>
+        </is>
+      </c>
+      <c r="E57" s="84" t="n"/>
+      <c r="F57" s="84" t="n"/>
+      <c r="G57" s="83" t="inlineStr">
+        <is>
+          <t>Canal local adicional</t>
+        </is>
+      </c>
+      <c r="H57" s="84" t="n"/>
+      <c r="I57" s="84" t="n"/>
+      <c r="J57" s="83" t="inlineStr">
+        <is>
+          <t>Catálogo genérico</t>
+        </is>
+      </c>
+      <c r="K57" s="84" t="n"/>
+      <c r="L57" s="84" t="n"/>
+      <c r="M57" s="83" t="inlineStr">
+        <is>
+          <t>clingenieria.co (https://clingenieria.co/)</t>
+        </is>
+      </c>
+      <c r="N57" s="84" t="n"/>
+      <c r="O57" s="84" t="n"/>
+    </row>
+    <row r="58" ht="38" customHeight="1"/>
+    <row r="59" ht="38" customHeight="1">
+      <c r="A59" s="81" t="inlineStr">
+        <is>
+          <t>5. Instalación</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="456" customHeight="1">
+      <c r="A60" s="85" t="inlineStr">
+        <is>
+          <t>5.1. Montaje a ras de muro exterior con marco perimetral sellado con silicona RTV neutra (compatible con hipoclorito; Chemical Resistance of RTV Silicone Sealants (PDF) (https://irp.cdn-website.com/63168859/files/uploaded/Chemical%20Resistance%20of%20RTV%20Silicone%20Sealants%20Chart.pdf), consulta 2026-07-23) y ferretería inox 316 (A4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="38" customHeight="1"/>
+    <row r="62" ht="114" customHeight="1">
       <c r="A62" s="85" t="inlineStr">
         <is>
-          <t>4. Candidatos comerciales</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="60" customHeight="1">
-      <c r="A63" s="87" t="inlineStr">
-        <is>
-          <t>Tabla 3. Candidatos (consulta 2026-07-23).</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="45" customHeight="1">
-      <c r="A64" s="82" t="inlineStr">
-        <is>
-          <t>Producto</t>
-        </is>
-      </c>
-      <c r="B64" s="82" t="n"/>
-      <c r="C64" s="82" t="n"/>
-      <c r="D64" s="82" t="inlineStr">
-        <is>
-          <t>Tipo / material</t>
-        </is>
-      </c>
-      <c r="E64" s="82" t="n"/>
-      <c r="F64" s="82" t="n"/>
-      <c r="G64" s="82" t="inlineStr">
-        <is>
-          <t>Pros</t>
-        </is>
-      </c>
-      <c r="H64" s="82" t="n"/>
-      <c r="I64" s="82" t="n"/>
-      <c r="J64" s="82" t="inlineStr">
-        <is>
-          <t>Contras</t>
-        </is>
-      </c>
-      <c r="K64" s="82" t="n"/>
-      <c r="L64" s="82" t="n"/>
-      <c r="M64" s="82" t="inlineStr">
-        <is>
-          <t>Fuente</t>
-        </is>
-      </c>
-      <c r="N64" s="82" t="n"/>
-      <c r="O64" s="82" t="n"/>
-    </row>
-    <row r="65" ht="240" customHeight="1">
-      <c r="A65" s="83" t="inlineStr">
-        <is>
-          <t>Titus 50F / 50R</t>
-        </is>
-      </c>
-      <c r="B65" s="84" t="n"/>
-      <c r="C65" s="84" t="n"/>
-      <c r="D65" s="83" t="inlineStr">
-        <is>
-          <t>Eggcrate ½ in; aluminio, con versión íntegramente inox de fábrica</t>
-        </is>
-      </c>
-      <c r="E65" s="84" t="n"/>
-      <c r="F65" s="84" t="n"/>
-      <c r="G65" s="83" t="inlineStr">
-        <is>
-          <t>«Highest free area of any return grille»; única opción inox de catálogo</t>
-        </is>
-      </c>
-      <c r="H65" s="84" t="n"/>
-      <c r="I65" s="84" t="n"/>
-      <c r="J65" s="83" t="inlineStr">
-        <is>
-          <t>Importación; tamaño 353×336 por pedido</t>
-        </is>
-      </c>
-      <c r="K65" s="84" t="n"/>
-      <c r="L65" s="84" t="n"/>
-      <c r="M65" s="83" t="inlineStr">
-        <is>
-          <t>Titus 50F (PDF) (https://www.titus-hvac.com/file/1228/50F_50Rrprod_specialized_2017.pdf)</t>
-        </is>
-      </c>
-      <c r="N65" s="84" t="n"/>
-      <c r="O65" s="84" t="n"/>
-    </row>
-    <row r="66" ht="255" customHeight="1">
-      <c r="A66" s="83" t="inlineStr">
-        <is>
-          <t>Krueger EGC5</t>
-        </is>
-      </c>
-      <c r="B66" s="84" t="n"/>
-      <c r="C66" s="84" t="n"/>
-      <c r="D66" s="83" t="inlineStr">
-        <is>
-          <t>Eggcrate ½ in; aluminio</t>
-        </is>
-      </c>
-      <c r="E66" s="84" t="n"/>
-      <c r="F66" s="84" t="n"/>
-      <c r="G66" s="83" t="inlineStr">
-        <is>
-          <t>Amplia gama de tamaños (6×4 in a 96×96 in)</t>
-        </is>
-      </c>
-      <c r="H66" s="84" t="n"/>
-      <c r="I66" s="84" t="n"/>
-      <c r="J66" s="83" t="inlineStr">
-        <is>
-          <t>Sin ejecución inox</t>
-        </is>
-      </c>
-      <c r="K66" s="84" t="n"/>
-      <c r="L66" s="84" t="n"/>
-      <c r="M66" s="83" t="inlineStr">
-        <is>
-          <t>Krueger EGC5 (https://www.krueger-hvac.com/Catalog%20Home/Grilles/Grilles%20-%20Return/EGC5)</t>
-        </is>
-      </c>
-      <c r="N66" s="84" t="n"/>
-      <c r="O66" s="84" t="n"/>
-    </row>
-    <row r="67" ht="240" customHeight="1">
-      <c r="A67" s="83" t="inlineStr">
-        <is>
-          <t>ProAire S.A.S (Bogotá)</t>
-        </is>
-      </c>
-      <c r="B67" s="84" t="n"/>
-      <c r="C67" s="84" t="n"/>
-      <c r="D67" s="83" t="inlineStr">
-        <is>
-          <t>Fabricación a medida con corte láser, inox 316</t>
-        </is>
-      </c>
-      <c r="E67" s="84" t="n"/>
-      <c r="F67" s="84" t="n"/>
-      <c r="G67" s="83" t="inlineStr">
-        <is>
-          <t>Medida exacta 353×336 y ejecución inox 316L local; vía recomendada</t>
-        </is>
-      </c>
-      <c r="H67" s="84" t="n"/>
-      <c r="I67" s="84" t="n"/>
-      <c r="J67" s="83" t="inlineStr">
-        <is>
-          <t>Submittal y Ak por confirmar con proveedor</t>
-        </is>
-      </c>
-      <c r="K67" s="84" t="n"/>
-      <c r="L67" s="84" t="n"/>
-      <c r="M67" s="83" t="inlineStr">
-        <is>
-          <t>proairecolombia.com (https://www.proairecolombia.com/productos/rejillas-y-difusores.html)</t>
-        </is>
-      </c>
-      <c r="N67" s="84" t="n"/>
-      <c r="O67" s="84" t="n"/>
-    </row>
-    <row r="68" ht="195" customHeight="1">
-      <c r="A68" s="83" t="inlineStr">
-        <is>
-          <t>Laminaire (Colombia)</t>
-        </is>
-      </c>
-      <c r="B68" s="84" t="n"/>
-      <c r="C68" s="84" t="n"/>
-      <c r="D68" s="83" t="inlineStr">
-        <is>
-          <t>Rejillas y difusores en aluminio a pedido</t>
-        </is>
-      </c>
-      <c r="E68" s="84" t="n"/>
-      <c r="F68" s="84" t="n"/>
-      <c r="G68" s="83" t="inlineStr">
-        <is>
-          <t>Fabricación local con software de selección; marco para malla a pedido</t>
-        </is>
-      </c>
-      <c r="H68" s="84" t="n"/>
-      <c r="I68" s="84" t="n"/>
-      <c r="J68" s="83" t="inlineStr">
-        <is>
-          <t>Confirmar ejecución inox</t>
-        </is>
-      </c>
-      <c r="K68" s="84" t="n"/>
-      <c r="L68" s="84" t="n"/>
-      <c r="M68" s="83" t="inlineStr">
-        <is>
-          <t>laminaire.net (https://laminaire.net/)</t>
-        </is>
-      </c>
-      <c r="N68" s="84" t="n"/>
-      <c r="O68" s="84" t="n"/>
-    </row>
-    <row r="69" ht="120" customHeight="1">
-      <c r="A69" s="83" t="inlineStr">
-        <is>
-          <t>CL Ingeniería (Bogotá)</t>
-        </is>
-      </c>
-      <c r="B69" s="84" t="n"/>
-      <c r="C69" s="84" t="n"/>
-      <c r="D69" s="83" t="inlineStr">
-        <is>
-          <t>Rejillas y accesorios HVAC</t>
-        </is>
-      </c>
-      <c r="E69" s="84" t="n"/>
-      <c r="F69" s="84" t="n"/>
-      <c r="G69" s="83" t="inlineStr">
-        <is>
-          <t>Canal local adicional</t>
-        </is>
-      </c>
-      <c r="H69" s="84" t="n"/>
-      <c r="I69" s="84" t="n"/>
-      <c r="J69" s="83" t="inlineStr">
-        <is>
-          <t>Catálogo genérico</t>
-        </is>
-      </c>
-      <c r="K69" s="84" t="n"/>
-      <c r="L69" s="84" t="n"/>
-      <c r="M69" s="83" t="inlineStr">
-        <is>
-          <t>clingenieria.co (https://clingenieria.co/)</t>
-        </is>
-      </c>
-      <c r="N69" s="84" t="n"/>
-      <c r="O69" s="84" t="n"/>
-    </row>
-    <row r="70" ht="15" customHeight="1"/>
-    <row r="71" ht="15" customHeight="1"/>
-    <row r="72" ht="45" customHeight="1">
-      <c r="A72" s="85" t="inlineStr">
-        <is>
-          <t>5. Instalación</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="150" customHeight="1">
-      <c r="A73" s="86" t="inlineStr">
-        <is>
-          <t>5.1. Montaje a ras de muro exterior con marco perimetral sellado con silicona RTV neutra (compatible con hipoclorito; Chemical Resistance of RTV Silicone Sealants (PDF) (https://irp.cdn-website.com/63168859/files/uploaded/Chemical%20Resistance%20of%20RTV%20Silicone%20Sealants%20Chart.pdf), consulta 2026-07-23) y ferretería inox 316 (A4).</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="15" customHeight="1"/>
-    <row r="75" ht="15" customHeight="1"/>
-    <row r="76" ht="15" customHeight="1"/>
-    <row r="77" ht="15" customHeight="1"/>
-    <row r="78" ht="15" customHeight="1"/>
-    <row r="79" ht="150" customHeight="1">
-      <c r="A79" s="86" t="inlineStr">
-        <is>
           <t>5.2. Las bocas exteriores se orientan preferentemente a sotavento respecto de las fuentes de cloro de la planta.</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="15" customHeight="1"/>
-    <row r="81" ht="165" customHeight="1">
-      <c r="A81" s="86" t="inlineStr">
+    <row r="63" ht="114" customHeight="1">
+      <c r="A63" s="85" t="inlineStr">
         <is>
           <t>5.3. Programa de limpieza de la malla según carga de polvo observada en comisionamiento (dato típico de operación).</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="15" customHeight="1"/>
-    <row r="83" ht="15" customHeight="1"/>
-    <row r="84" ht="60" customHeight="1">
-      <c r="A84" s="85" t="inlineStr">
+    <row r="64" ht="38" customHeight="1"/>
+    <row r="65" ht="76" customHeight="1">
+      <c r="A65" s="81" t="inlineStr">
         <is>
           <t>6. Normas aplicables</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="165" customHeight="1">
-      <c r="A85" s="86" t="inlineStr">
+    <row r="66" ht="494" customHeight="1">
+      <c r="A66" s="85" t="inlineStr">
         <is>
           <t>6.1. ASHRAE 70 (método de ensayo y reporte de desempeño de rejillas); correlación de área libre para transferencia de aire según Building Science BA-0006 (https://buildingscience.com/sites/default/files/migrate/pdf/BA-0006_Discuss_transfer_grilles.pdf) (consulta 2026-07-23); ISO 12944 / NACE-AMPP para la selección de materiales en el ambiente clorado.</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="15" customHeight="1"/>
-    <row r="87" ht="15" customHeight="1"/>
-    <row r="88" ht="15" customHeight="1"/>
-    <row r="89" ht="15" customHeight="1"/>
-    <row r="90" ht="15" customHeight="1"/>
+    <row r="67" ht="38" customHeight="1"/>
   </sheetData>
-  <mergeCells count="104">
-    <mergeCell ref="I52:O52"/>
-    <mergeCell ref="A85:O90"/>
-    <mergeCell ref="D66:F66"/>
-    <mergeCell ref="A49:H49"/>
+  <mergeCells count="100">
+    <mergeCell ref="I44:O44"/>
+    <mergeCell ref="D53:F53"/>
+    <mergeCell ref="A50:O50"/>
+    <mergeCell ref="A57:C57"/>
     <mergeCell ref="N3:O3"/>
-    <mergeCell ref="A19:O24"/>
-    <mergeCell ref="G65:I65"/>
-    <mergeCell ref="J66:L66"/>
+    <mergeCell ref="A25:H25"/>
     <mergeCell ref="I30:O30"/>
-    <mergeCell ref="A79:O80"/>
     <mergeCell ref="N5:O5"/>
     <mergeCell ref="I46:O46"/>
     <mergeCell ref="C2:L3"/>
-    <mergeCell ref="A50:H50"/>
-    <mergeCell ref="A55:H55"/>
-    <mergeCell ref="M66:O66"/>
-    <mergeCell ref="A44:O44"/>
-    <mergeCell ref="I54:O54"/>
-    <mergeCell ref="A32:H32"/>
-    <mergeCell ref="I32:O32"/>
-    <mergeCell ref="M68:O68"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="J52:L52"/>
+    <mergeCell ref="M53:O53"/>
+    <mergeCell ref="G52:I52"/>
+    <mergeCell ref="I41:O41"/>
+    <mergeCell ref="M55:O55"/>
     <mergeCell ref="A29:H29"/>
-    <mergeCell ref="M67:O67"/>
+    <mergeCell ref="A38:H38"/>
+    <mergeCell ref="M52:O52"/>
+    <mergeCell ref="I43:O43"/>
     <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A69:C69"/>
-    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A44:H44"/>
+    <mergeCell ref="I24:O24"/>
     <mergeCell ref="B1:B5"/>
-    <mergeCell ref="I33:O33"/>
-    <mergeCell ref="M69:O69"/>
-    <mergeCell ref="A66:C66"/>
+    <mergeCell ref="D57:F57"/>
+    <mergeCell ref="A40:H40"/>
     <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A51:H51"/>
-    <mergeCell ref="J65:L65"/>
-    <mergeCell ref="A57:O60"/>
-    <mergeCell ref="G69:I69"/>
-    <mergeCell ref="I35:O35"/>
-    <mergeCell ref="A84:O84"/>
+    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="A55:C55"/>
     <mergeCell ref="I10:O10"/>
-    <mergeCell ref="A18:O18"/>
-    <mergeCell ref="I50:O50"/>
     <mergeCell ref="N2:O2"/>
-    <mergeCell ref="G64:I64"/>
-    <mergeCell ref="D68:F68"/>
-    <mergeCell ref="A62:O62"/>
+    <mergeCell ref="G55:I55"/>
+    <mergeCell ref="M57:O57"/>
+    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="D55:F55"/>
     <mergeCell ref="I11:O11"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="A72:O72"/>
-    <mergeCell ref="A67:C67"/>
-    <mergeCell ref="A47:H47"/>
-    <mergeCell ref="I47:O47"/>
-    <mergeCell ref="D69:F69"/>
-    <mergeCell ref="J67:L67"/>
+    <mergeCell ref="I45:O45"/>
+    <mergeCell ref="G54:I54"/>
+    <mergeCell ref="D54:F54"/>
+    <mergeCell ref="A42:H42"/>
+    <mergeCell ref="M56:O56"/>
+    <mergeCell ref="G56:I56"/>
+    <mergeCell ref="I28:O28"/>
+    <mergeCell ref="A59:O59"/>
+    <mergeCell ref="I37:O37"/>
     <mergeCell ref="N6:O6"/>
-    <mergeCell ref="J69:L69"/>
+    <mergeCell ref="A28:H28"/>
     <mergeCell ref="N4:O4"/>
-    <mergeCell ref="A48:H48"/>
+    <mergeCell ref="J53:L53"/>
+    <mergeCell ref="I23:O23"/>
     <mergeCell ref="A30:H30"/>
-    <mergeCell ref="G66:I66"/>
-    <mergeCell ref="I51:O51"/>
-    <mergeCell ref="G68:I68"/>
-    <mergeCell ref="A54:H54"/>
-    <mergeCell ref="I34:O34"/>
-    <mergeCell ref="I49:O49"/>
-    <mergeCell ref="A73:O78"/>
-    <mergeCell ref="I36:O36"/>
-    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="G53:I53"/>
+    <mergeCell ref="J55:L55"/>
+    <mergeCell ref="J54:L54"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="J56:L56"/>
+    <mergeCell ref="A17:O17"/>
+    <mergeCell ref="A60:O61"/>
+    <mergeCell ref="I27:O27"/>
+    <mergeCell ref="A35:O35"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A66:O67"/>
     <mergeCell ref="A1:A5"/>
     <mergeCell ref="A9:O9"/>
     <mergeCell ref="C1:L1"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A53:H53"/>
-    <mergeCell ref="I53:O53"/>
-    <mergeCell ref="A35:H35"/>
+    <mergeCell ref="J57:L57"/>
+    <mergeCell ref="A18:O19"/>
     <mergeCell ref="A10:H10"/>
     <mergeCell ref="I12:O12"/>
-    <mergeCell ref="I55:O55"/>
-    <mergeCell ref="J68:L68"/>
-    <mergeCell ref="A34:H34"/>
+    <mergeCell ref="A32:O33"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A65:O65"/>
+    <mergeCell ref="A39:H39"/>
     <mergeCell ref="I14:O14"/>
-    <mergeCell ref="A81:O82"/>
-    <mergeCell ref="I48:O48"/>
+    <mergeCell ref="I39:O39"/>
+    <mergeCell ref="M54:O54"/>
+    <mergeCell ref="G57:I57"/>
+    <mergeCell ref="A56:C56"/>
     <mergeCell ref="I29:O29"/>
-    <mergeCell ref="A36:H36"/>
     <mergeCell ref="A11:H11"/>
-    <mergeCell ref="M65:O65"/>
-    <mergeCell ref="M64:O64"/>
+    <mergeCell ref="I38:O38"/>
+    <mergeCell ref="A45:H45"/>
+    <mergeCell ref="A21:O21"/>
     <mergeCell ref="I13:O13"/>
-    <mergeCell ref="A26:O26"/>
-    <mergeCell ref="I31:O31"/>
+    <mergeCell ref="I40:O40"/>
+    <mergeCell ref="D56:F56"/>
     <mergeCell ref="I15:O15"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A37:H37"/>
     <mergeCell ref="A46:H46"/>
     <mergeCell ref="N1:O1"/>
     <mergeCell ref="A12:H12"/>
-    <mergeCell ref="D64:F64"/>
-    <mergeCell ref="A68:C68"/>
+    <mergeCell ref="I26:O26"/>
     <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A27:O28"/>
-    <mergeCell ref="J64:L64"/>
-    <mergeCell ref="A38:O42"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="I25:O25"/>
     <mergeCell ref="C4:L6"/>
-    <mergeCell ref="G67:I67"/>
-    <mergeCell ref="D65:F65"/>
-    <mergeCell ref="A52:H52"/>
-    <mergeCell ref="A65:C65"/>
+    <mergeCell ref="A43:H43"/>
+    <mergeCell ref="D52:F52"/>
+    <mergeCell ref="I42:O42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Emisiones/3.0 HV-HOJAS DE DATOS/P2437-HV-DTS-003.xlsx
+++ b/Emisiones/3.0 HV-HOJAS DE DATOS/P2437-HV-DTS-003.xlsx
@@ -3708,28 +3708,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O67"/>
+  <dimension ref="A1:O63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="49" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="35" customWidth="1" min="9" max="9"/>
+    <col width="35" customWidth="1" min="10" max="10"/>
+    <col width="35" customWidth="1" min="11" max="11"/>
+    <col width="35" customWidth="1" min="12" max="12"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="14" max="14"/>
+    <col width="35" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="17" max="17"/>
-    <col width="13" customWidth="1" min="18" max="18"/>
-    <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
     <col width="13" customWidth="1" min="23" max="23"/>
     <col width="13" customWidth="1" min="24" max="24"/>
     <col width="13" customWidth="1" min="25" max="25"/>
@@ -3737,10 +3736,9 @@
     <col width="13" customWidth="1" min="27" max="27"/>
     <col width="13" customWidth="1" min="28" max="28"/>
     <col width="13" customWidth="1" min="29" max="29"/>
-    <col width="13" customWidth="1" min="30" max="30"/>
-    <col width="13" customWidth="1" min="32" max="32"/>
     <col width="13" customWidth="1" min="33" max="33"/>
     <col width="13" customWidth="1" min="35" max="35"/>
+    <col width="13" customWidth="1" min="36" max="36"/>
     <col width="13" customWidth="1" min="37" max="37"/>
     <col width="13" customWidth="1" min="38" max="38"/>
     <col width="13" customWidth="1" min="39" max="39"/>
@@ -3749,21 +3747,15 @@
     <col width="13" customWidth="1" min="42" max="42"/>
     <col width="13" customWidth="1" min="43" max="43"/>
     <col width="13" customWidth="1" min="44" max="44"/>
-    <col width="13" customWidth="1" min="45" max="45"/>
-    <col width="13" customWidth="1" min="46" max="46"/>
+    <col width="13" customWidth="1" min="48" max="48"/>
     <col width="13" customWidth="1" min="50" max="50"/>
+    <col width="13" customWidth="1" min="51" max="51"/>
     <col width="13" customWidth="1" min="52" max="52"/>
     <col width="13" customWidth="1" min="53" max="53"/>
     <col width="13" customWidth="1" min="54" max="54"/>
     <col width="13" customWidth="1" min="55" max="55"/>
-    <col width="13" customWidth="1" min="56" max="56"/>
     <col width="13" customWidth="1" min="57" max="57"/>
-    <col width="13" customWidth="1" min="59" max="59"/>
-    <col width="13" customWidth="1" min="60" max="60"/>
-    <col width="13" customWidth="1" min="61" max="61"/>
-    <col width="13" customWidth="1" min="65" max="65"/>
-    <col width="13" customWidth="1" min="66" max="66"/>
-    <col width="13" customWidth="1" min="67" max="67"/>
+    <col width="13" customWidth="1" min="62" max="62"/>
   </cols>
   <sheetData>
     <row r="1" ht="29.25" customHeight="1">
@@ -3973,14 +3965,14 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" ht="228" customHeight="1">
+    <row r="9" ht="100" customHeight="1">
       <c r="A9" s="81" t="inlineStr">
         <is>
           <t>Hoja de datos: rejillas de descarga con malla anti-insectos</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="38" customHeight="1">
+    <row r="10" ht="50" customHeight="1">
       <c r="A10" s="82" t="inlineStr">
         <is>
           <t>Campo</t>
@@ -4005,7 +3997,7 @@
       <c r="N10" s="82" t="n"/>
       <c r="O10" s="82" t="n"/>
     </row>
-    <row r="11" ht="38" customHeight="1">
+    <row r="11" ht="50" customHeight="1">
       <c r="A11" s="83" t="inlineStr">
         <is>
           <t>Código</t>
@@ -4030,7 +4022,7 @@
       <c r="N11" s="84" t="n"/>
       <c r="O11" s="84" t="n"/>
     </row>
-    <row r="12" ht="38" customHeight="1">
+    <row r="12" ht="50" customHeight="1">
       <c r="A12" s="83" t="inlineStr">
         <is>
           <t>Revisión</t>
@@ -4055,7 +4047,7 @@
       <c r="N12" s="84" t="n"/>
       <c r="O12" s="84" t="n"/>
     </row>
-    <row r="13" ht="38" customHeight="1">
+    <row r="13" ht="50" customHeight="1">
       <c r="A13" s="83" t="inlineStr">
         <is>
           <t>Fecha</t>
@@ -4080,7 +4072,7 @@
       <c r="N13" s="84" t="n"/>
       <c r="O13" s="84" t="n"/>
     </row>
-    <row r="14" ht="152" customHeight="1">
+    <row r="14" ht="100" customHeight="1">
       <c r="A14" s="83" t="inlineStr">
         <is>
           <t>Proyecto</t>
@@ -4105,7 +4097,7 @@
       <c r="N14" s="84" t="n"/>
       <c r="O14" s="84" t="n"/>
     </row>
-    <row r="15" ht="114" customHeight="1">
+    <row r="15" ht="100" customHeight="1">
       <c r="A15" s="83" t="inlineStr">
         <is>
           <t>Etiqueta de equipo</t>
@@ -4130,66 +4122,90 @@
       <c r="N15" s="84" t="n"/>
       <c r="O15" s="84" t="n"/>
     </row>
-    <row r="16" ht="38" customHeight="1"/>
-    <row r="17" ht="38" customHeight="1">
+    <row r="16" ht="50" customHeight="1"/>
+    <row r="17" ht="50" customHeight="1">
       <c r="A17" s="81" t="inlineStr">
         <is>
           <t>1. Servicio</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="494" customHeight="1">
+    <row r="18" ht="500" customHeight="1">
       <c r="A18" s="85" t="inlineStr">
         <is>
           <t>1.1. Descarga libre a la atmósfera del caudal de ventilación del laboratorio, a través de la envolvente del recinto. Las rejillas son la trayectoria de salida permanente del aire y, con el sistema detenido, una vía potencial de ingreso: por ello incorporan malla anti-insectos. Ambiente exterior corrosivo (atmósfera clorada de planta de hipoclorito de calcio).</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="38" customHeight="1"/>
-    <row r="20" ht="38" customHeight="1"/>
-    <row r="21" ht="114" customHeight="1">
-      <c r="A21" s="81" t="inlineStr">
+    <row r="19" ht="50" customHeight="1"/>
+    <row r="20" ht="150" customHeight="1">
+      <c r="A20" s="81" t="inlineStr">
         <is>
           <t>2. Condiciones de operación y desempeño</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="76" customHeight="1">
-      <c r="A22" s="86" t="inlineStr">
+    <row r="21" ht="100" customHeight="1">
+      <c r="A21" s="86" t="inlineStr">
         <is>
           <t>Tabla 1. Condiciones de diseño (valores congelados de la memoria de cálculo).</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="38" customHeight="1">
-      <c r="A23" s="82" t="inlineStr">
+    <row r="22" ht="50" customHeight="1">
+      <c r="A22" s="82" t="inlineStr">
         <is>
           <t>Parámetro</t>
         </is>
       </c>
-      <c r="B23" s="82" t="n"/>
-      <c r="C23" s="82" t="n"/>
-      <c r="D23" s="82" t="n"/>
-      <c r="E23" s="82" t="n"/>
-      <c r="F23" s="82" t="n"/>
-      <c r="G23" s="82" t="n"/>
-      <c r="H23" s="82" t="n"/>
-      <c r="I23" s="82" t="inlineStr">
+      <c r="B22" s="82" t="n"/>
+      <c r="C22" s="82" t="n"/>
+      <c r="D22" s="82" t="n"/>
+      <c r="E22" s="82" t="n"/>
+      <c r="F22" s="82" t="n"/>
+      <c r="G22" s="82" t="n"/>
+      <c r="H22" s="82" t="n"/>
+      <c r="I22" s="82" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
       </c>
-      <c r="J23" s="82" t="n"/>
-      <c r="K23" s="82" t="n"/>
-      <c r="L23" s="82" t="n"/>
-      <c r="M23" s="82" t="n"/>
-      <c r="N23" s="82" t="n"/>
-      <c r="O23" s="82" t="n"/>
-    </row>
-    <row r="24" ht="38" customHeight="1">
+      <c r="J22" s="82" t="n"/>
+      <c r="K22" s="82" t="n"/>
+      <c r="L22" s="82" t="n"/>
+      <c r="M22" s="82" t="n"/>
+      <c r="N22" s="82" t="n"/>
+      <c r="O22" s="82" t="n"/>
+    </row>
+    <row r="23" ht="50" customHeight="1">
+      <c r="A23" s="83" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="B23" s="84" t="n"/>
+      <c r="C23" s="84" t="n"/>
+      <c r="D23" s="84" t="n"/>
+      <c r="E23" s="84" t="n"/>
+      <c r="F23" s="84" t="n"/>
+      <c r="G23" s="84" t="n"/>
+      <c r="H23" s="84" t="n"/>
+      <c r="I23" s="83" t="inlineStr">
+        <is>
+          <t>3 unidades</t>
+        </is>
+      </c>
+      <c r="J23" s="84" t="n"/>
+      <c r="K23" s="84" t="n"/>
+      <c r="L23" s="84" t="n"/>
+      <c r="M23" s="84" t="n"/>
+      <c r="N23" s="84" t="n"/>
+      <c r="O23" s="84" t="n"/>
+    </row>
+    <row r="24" ht="150" customHeight="1">
       <c r="A24" s="83" t="inlineStr">
         <is>
-          <t>Cantidad</t>
+          <t>Dimensiones faciales (unitarias)</t>
         </is>
       </c>
       <c r="B24" s="84" t="n"/>
@@ -4201,7 +4217,7 @@
       <c r="H24" s="84" t="n"/>
       <c r="I24" s="83" t="inlineStr">
         <is>
-          <t>3 unidades</t>
+          <t>353×336 mm (área facial 0.1187 m²)</t>
         </is>
       </c>
       <c r="J24" s="84" t="n"/>
@@ -4211,10 +4227,10 @@
       <c r="N24" s="84" t="n"/>
       <c r="O24" s="84" t="n"/>
     </row>
-    <row r="25" ht="114" customHeight="1">
+    <row r="25" ht="100" customHeight="1">
       <c r="A25" s="83" t="inlineStr">
         <is>
-          <t>Dimensiones faciales (unitarias)</t>
+          <t>Caudal total de descarga</t>
         </is>
       </c>
       <c r="B25" s="84" t="n"/>
@@ -4226,7 +4242,7 @@
       <c r="H25" s="84" t="n"/>
       <c r="I25" s="83" t="inlineStr">
         <is>
-          <t>353×336 mm (área facial 0.1187 m²)</t>
+          <t>3 840 m³/h (1.0667 m³/s)</t>
         </is>
       </c>
       <c r="J25" s="84" t="n"/>
@@ -4236,10 +4252,10 @@
       <c r="N25" s="84" t="n"/>
       <c r="O25" s="84" t="n"/>
     </row>
-    <row r="26" ht="76" customHeight="1">
+    <row r="26" ht="100" customHeight="1">
       <c r="A26" s="83" t="inlineStr">
         <is>
-          <t>Caudal total de descarga</t>
+          <t>Velocidad facial</t>
         </is>
       </c>
       <c r="B26" s="84" t="n"/>
@@ -4251,7 +4267,7 @@
       <c r="H26" s="84" t="n"/>
       <c r="I26" s="83" t="inlineStr">
         <is>
-          <t>3 840 m³/h (1.0667 m³/s)</t>
+          <t>3 m/s</t>
         </is>
       </c>
       <c r="J26" s="84" t="n"/>
@@ -4261,10 +4277,10 @@
       <c r="N26" s="84" t="n"/>
       <c r="O26" s="84" t="n"/>
     </row>
-    <row r="27" ht="76" customHeight="1">
+    <row r="27" ht="200" customHeight="1">
       <c r="A27" s="83" t="inlineStr">
         <is>
-          <t>Velocidad facial</t>
+          <t>ΔP unitaria (cierre de orificio, C_d = 0.60, en el sitio)</t>
         </is>
       </c>
       <c r="B27" s="84" t="n"/>
@@ -4276,7 +4292,7 @@
       <c r="H27" s="84" t="n"/>
       <c r="I27" s="83" t="inlineStr">
         <is>
-          <t>3 m/s</t>
+          <t>11 Pa</t>
         </is>
       </c>
       <c r="J27" s="84" t="n"/>
@@ -4286,10 +4302,10 @@
       <c r="N27" s="84" t="n"/>
       <c r="O27" s="84" t="n"/>
     </row>
-    <row r="28" ht="152" customHeight="1">
+    <row r="28" ht="200" customHeight="1">
       <c r="A28" s="83" t="inlineStr">
         <is>
-          <t>ΔP unitaria (cierre de orificio, C_d = 0.60, en el sitio)</t>
+          <t>ΔP equivalente a densidad estándar (ρ = 1.2 kg/m³)</t>
         </is>
       </c>
       <c r="B28" s="84" t="n"/>
@@ -4301,7 +4317,7 @@
       <c r="H28" s="84" t="n"/>
       <c r="I28" s="83" t="inlineStr">
         <is>
-          <t>11 Pa</t>
+          <t>15 Pa</t>
         </is>
       </c>
       <c r="J28" s="84" t="n"/>
@@ -4311,10 +4327,10 @@
       <c r="N28" s="84" t="n"/>
       <c r="O28" s="84" t="n"/>
     </row>
-    <row r="29" ht="152" customHeight="1">
+    <row r="29" ht="150" customHeight="1">
       <c r="A29" s="83" t="inlineStr">
         <is>
-          <t>ΔP equivalente a densidad estándar (ρ = 1.2 kg/m³)</t>
+          <t>Densidad del aire de diseño</t>
         </is>
       </c>
       <c r="B29" s="84" t="n"/>
@@ -4326,7 +4342,7 @@
       <c r="H29" s="84" t="n"/>
       <c r="I29" s="83" t="inlineStr">
         <is>
-          <t>15 Pa</t>
+          <t>0.88 kg/m³ (2 558 msnm, 74.1 kPa)</t>
         </is>
       </c>
       <c r="J29" s="84" t="n"/>
@@ -4336,84 +4352,108 @@
       <c r="N29" s="84" t="n"/>
       <c r="O29" s="84" t="n"/>
     </row>
-    <row r="30" ht="114" customHeight="1">
-      <c r="A30" s="83" t="inlineStr">
-        <is>
-          <t>Densidad del aire de diseño</t>
-        </is>
-      </c>
-      <c r="B30" s="84" t="n"/>
-      <c r="C30" s="84" t="n"/>
-      <c r="D30" s="84" t="n"/>
-      <c r="E30" s="84" t="n"/>
-      <c r="F30" s="84" t="n"/>
-      <c r="G30" s="84" t="n"/>
-      <c r="H30" s="84" t="n"/>
-      <c r="I30" s="83" t="inlineStr">
-        <is>
-          <t>0.88 kg/m³ (2 558 msnm, 74.1 kPa)</t>
-        </is>
-      </c>
-      <c r="J30" s="84" t="n"/>
-      <c r="K30" s="84" t="n"/>
-      <c r="L30" s="84" t="n"/>
-      <c r="M30" s="84" t="n"/>
-      <c r="N30" s="84" t="n"/>
-      <c r="O30" s="84" t="n"/>
-    </row>
-    <row r="31" ht="38" customHeight="1"/>
-    <row r="32" ht="418" customHeight="1">
-      <c r="A32" s="85" t="inlineStr">
+    <row r="30" ht="50" customHeight="1"/>
+    <row r="31" ht="400" customHeight="1">
+      <c r="A31" s="85" t="inlineStr">
         <is>
           <t>2.1. Nota de contexto: la ΔP unitaria de 11 Pa (cierre de orificio, C_d = 0.60, a 3 m/s) es la pérdida de descarga libre a la atmósfera y se suma a la caída de presión de la etapa filtrante para definir el punto de trabajo del ventilador; no existe consigna de presión interior que sostener.</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="38" customHeight="1"/>
-    <row r="34" ht="38" customHeight="1"/>
-    <row r="35" ht="114" customHeight="1">
-      <c r="A35" s="81" t="inlineStr">
+    <row r="32" ht="50" customHeight="1"/>
+    <row r="33" ht="150" customHeight="1">
+      <c r="A33" s="81" t="inlineStr">
         <is>
           <t>3. Construcción y áreas netas</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="38" customHeight="1">
-      <c r="A36" s="86" t="inlineStr">
+    <row r="34" ht="50" customHeight="1">
+      <c r="A34" s="86" t="inlineStr">
         <is>
           <t>Tabla 2. Especificación constructiva.</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="38" customHeight="1">
-      <c r="A37" s="82" t="inlineStr">
+    <row r="35" ht="50" customHeight="1">
+      <c r="A35" s="82" t="inlineStr">
         <is>
           <t>Característica</t>
         </is>
       </c>
-      <c r="B37" s="82" t="n"/>
-      <c r="C37" s="82" t="n"/>
-      <c r="D37" s="82" t="n"/>
-      <c r="E37" s="82" t="n"/>
-      <c r="F37" s="82" t="n"/>
-      <c r="G37" s="82" t="n"/>
-      <c r="H37" s="82" t="n"/>
-      <c r="I37" s="82" t="inlineStr">
+      <c r="B35" s="82" t="n"/>
+      <c r="C35" s="82" t="n"/>
+      <c r="D35" s="82" t="n"/>
+      <c r="E35" s="82" t="n"/>
+      <c r="F35" s="82" t="n"/>
+      <c r="G35" s="82" t="n"/>
+      <c r="H35" s="82" t="n"/>
+      <c r="I35" s="82" t="inlineStr">
         <is>
           <t>Especificación</t>
         </is>
       </c>
-      <c r="J37" s="82" t="n"/>
-      <c r="K37" s="82" t="n"/>
-      <c r="L37" s="82" t="n"/>
-      <c r="M37" s="82" t="n"/>
-      <c r="N37" s="82" t="n"/>
-      <c r="O37" s="82" t="n"/>
-    </row>
-    <row r="38" ht="152" customHeight="1">
+      <c r="J35" s="82" t="n"/>
+      <c r="K35" s="82" t="n"/>
+      <c r="L35" s="82" t="n"/>
+      <c r="M35" s="82" t="n"/>
+      <c r="N35" s="82" t="n"/>
+      <c r="O35" s="82" t="n"/>
+    </row>
+    <row r="36" ht="200" customHeight="1">
+      <c r="A36" s="83" t="inlineStr">
+        <is>
+          <t>Tipo de núcleo</t>
+        </is>
+      </c>
+      <c r="B36" s="84" t="n"/>
+      <c r="C36" s="84" t="n"/>
+      <c r="D36" s="84" t="n"/>
+      <c r="E36" s="84" t="n"/>
+      <c r="F36" s="84" t="n"/>
+      <c r="G36" s="84" t="n"/>
+      <c r="H36" s="84" t="n"/>
+      <c r="I36" s="83" t="inlineStr">
+        <is>
+          <t>Eggcrate (panal) ½×½×½ in (12.7 mm), máxima área libre</t>
+        </is>
+      </c>
+      <c r="J36" s="84" t="n"/>
+      <c r="K36" s="84" t="n"/>
+      <c r="L36" s="84" t="n"/>
+      <c r="M36" s="84" t="n"/>
+      <c r="N36" s="84" t="n"/>
+      <c r="O36" s="84" t="n"/>
+    </row>
+    <row r="37" ht="600" customHeight="1">
+      <c r="A37" s="83" t="inlineStr">
+        <is>
+          <t>Área libre del núcleo</t>
+        </is>
+      </c>
+      <c r="B37" s="84" t="n"/>
+      <c r="C37" s="84" t="n"/>
+      <c r="D37" s="84" t="n"/>
+      <c r="E37" s="84" t="n"/>
+      <c r="F37" s="84" t="n"/>
+      <c r="G37" s="84" t="n"/>
+      <c r="H37" s="84" t="n"/>
+      <c r="I37" s="83" t="inlineStr">
+        <is>
+          <t>≥ 90 % (cifra repetida en catálogos del tipo; Airfoil RC-FCR5 (https://airfoil.com.au/product/removable-core-fixing-clip-eggcrate-grille-rc-fcr5/), consulta 2026-07-23)</t>
+        </is>
+      </c>
+      <c r="J37" s="84" t="n"/>
+      <c r="K37" s="84" t="n"/>
+      <c r="L37" s="84" t="n"/>
+      <c r="M37" s="84" t="n"/>
+      <c r="N37" s="84" t="n"/>
+      <c r="O37" s="84" t="n"/>
+    </row>
+    <row r="38" ht="950" customHeight="1">
       <c r="A38" s="83" t="inlineStr">
         <is>
-          <t>Tipo de núcleo</t>
+          <t>Malla anti-insectos</t>
         </is>
       </c>
       <c r="B38" s="84" t="n"/>
@@ -4425,7 +4465,7 @@
       <c r="H38" s="84" t="n"/>
       <c r="I38" s="83" t="inlineStr">
         <is>
-          <t>Eggcrate (panal) ½×½×½ in (12.7 mm), máxima área libre</t>
+          <t>Tejido 18×18, abertura ≈1 mm, alambre 0.45 mm, área abierta ≥ 48 % (tabla Industrial Metal Mesh (https://www.industrialmetalmesh.com/sale-54819921-micron-304-316l-stainless-steel-wire-mesh-screen-filter-mesh.html), consulta 2026-07-23); excluye insectos comunes</t>
         </is>
       </c>
       <c r="J38" s="84" t="n"/>
@@ -4435,10 +4475,10 @@
       <c r="N38" s="84" t="n"/>
       <c r="O38" s="84" t="n"/>
     </row>
-    <row r="39" ht="456" customHeight="1">
+    <row r="39" ht="200" customHeight="1">
       <c r="A39" s="83" t="inlineStr">
         <is>
-          <t>Área libre del núcleo</t>
+          <t>Área neta combinada (núcleo + malla)</t>
         </is>
       </c>
       <c r="B39" s="84" t="n"/>
@@ -4450,7 +4490,7 @@
       <c r="H39" s="84" t="n"/>
       <c r="I39" s="83" t="inlineStr">
         <is>
-          <t>≥ 90 % (cifra repetida en catálogos del tipo; Airfoil RC-FCR5 (https://airfoil.com.au/product/removable-core-fixing-clip-eggcrate-grille-rc-fcr5/), consulta 2026-07-23)</t>
+          <t>≈ 45 % del área facial (dato típico: 0.90 × 0.50)</t>
         </is>
       </c>
       <c r="J39" s="84" t="n"/>
@@ -4460,10 +4500,10 @@
       <c r="N39" s="84" t="n"/>
       <c r="O39" s="84" t="n"/>
     </row>
-    <row r="40" ht="722" customHeight="1">
+    <row r="40" ht="250" customHeight="1">
       <c r="A40" s="83" t="inlineStr">
         <is>
-          <t>Malla anti-insectos</t>
+          <t>Material de la rejilla</t>
         </is>
       </c>
       <c r="B40" s="84" t="n"/>
@@ -4475,7 +4515,7 @@
       <c r="H40" s="84" t="n"/>
       <c r="I40" s="83" t="inlineStr">
         <is>
-          <t>Tejido 18×18, abertura ≈1 mm, alambre 0.45 mm, área abierta ≥ 48 % (tabla Industrial Metal Mesh (https://www.industrialmetalmesh.com/sale-54819921-micron-304-316l-stainless-steel-wire-mesh-screen-filter-mesh.html), consulta 2026-07-23); excluye insectos comunes</t>
+          <t>Inox 316L (primera opción) o aluminio anodizado 6063-T5 (alternativa)</t>
         </is>
       </c>
       <c r="J40" s="84" t="n"/>
@@ -4485,10 +4525,10 @@
       <c r="N40" s="84" t="n"/>
       <c r="O40" s="84" t="n"/>
     </row>
-    <row r="41" ht="152" customHeight="1">
+    <row r="41" ht="100" customHeight="1">
       <c r="A41" s="83" t="inlineStr">
         <is>
-          <t>Área neta combinada (núcleo + malla)</t>
+          <t>Material de la malla</t>
         </is>
       </c>
       <c r="B41" s="84" t="n"/>
@@ -4500,7 +4540,7 @@
       <c r="H41" s="84" t="n"/>
       <c r="I41" s="83" t="inlineStr">
         <is>
-          <t>≈ 45 % del área facial (dato típico: 0.90 × 0.50)</t>
+          <t>Inox 316</t>
         </is>
       </c>
       <c r="J41" s="84" t="n"/>
@@ -4510,10 +4550,10 @@
       <c r="N41" s="84" t="n"/>
       <c r="O41" s="84" t="n"/>
     </row>
-    <row r="42" ht="190" customHeight="1">
+    <row r="42" ht="150" customHeight="1">
       <c r="A42" s="83" t="inlineStr">
         <is>
-          <t>Material de la rejilla</t>
+          <t>Montaje de la malla</t>
         </is>
       </c>
       <c r="B42" s="84" t="n"/>
@@ -4525,7 +4565,7 @@
       <c r="H42" s="84" t="n"/>
       <c r="I42" s="83" t="inlineStr">
         <is>
-          <t>Inox 316L (primera opción) o aluminio anodizado 6063-T5 (alternativa)</t>
+          <t>Marco desmontable para limpieza periódica</t>
         </is>
       </c>
       <c r="J42" s="84" t="n"/>
@@ -4535,10 +4575,10 @@
       <c r="N42" s="84" t="n"/>
       <c r="O42" s="84" t="n"/>
     </row>
-    <row r="43" ht="76" customHeight="1">
+    <row r="43" ht="350" customHeight="1">
       <c r="A43" s="83" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Par galvánico</t>
         </is>
       </c>
       <c r="B43" s="84" t="n"/>
@@ -4550,7 +4590,7 @@
       <c r="H43" s="84" t="n"/>
       <c r="I43" s="83" t="inlineStr">
         <is>
-          <t>Inox 316</t>
+          <t>Si se combina marco de aluminio con malla inox, aislamiento dieléctrico (dato típico de ingeniería)</t>
         </is>
       </c>
       <c r="J43" s="84" t="n"/>
@@ -4560,10 +4600,10 @@
       <c r="N43" s="84" t="n"/>
       <c r="O43" s="84" t="n"/>
     </row>
-    <row r="44" ht="114" customHeight="1">
+    <row r="44" ht="150" customHeight="1">
       <c r="A44" s="83" t="inlineStr">
         <is>
-          <t>Montaje de la malla</t>
+          <t>Ensayo de desempeño</t>
         </is>
       </c>
       <c r="B44" s="84" t="n"/>
@@ -4575,7 +4615,7 @@
       <c r="H44" s="84" t="n"/>
       <c r="I44" s="83" t="inlineStr">
         <is>
-          <t>Marco desmontable para limpieza periódica</t>
+          <t>ASHRAE 70 (medición de rejillas)</t>
         </is>
       </c>
       <c r="J44" s="84" t="n"/>
@@ -4585,360 +4625,306 @@
       <c r="N44" s="84" t="n"/>
       <c r="O44" s="84" t="n"/>
     </row>
-    <row r="45" ht="266" customHeight="1">
-      <c r="A45" s="83" t="inlineStr">
-        <is>
-          <t>Par galvánico</t>
-        </is>
-      </c>
-      <c r="B45" s="84" t="n"/>
-      <c r="C45" s="84" t="n"/>
-      <c r="D45" s="84" t="n"/>
-      <c r="E45" s="84" t="n"/>
-      <c r="F45" s="84" t="n"/>
-      <c r="G45" s="84" t="n"/>
-      <c r="H45" s="84" t="n"/>
-      <c r="I45" s="83" t="inlineStr">
-        <is>
-          <t>Si se combina marco de aluminio con malla inox, aislamiento dieléctrico (dato típico de ingeniería)</t>
-        </is>
-      </c>
-      <c r="J45" s="84" t="n"/>
-      <c r="K45" s="84" t="n"/>
-      <c r="L45" s="84" t="n"/>
-      <c r="M45" s="84" t="n"/>
-      <c r="N45" s="84" t="n"/>
-      <c r="O45" s="84" t="n"/>
-    </row>
-    <row r="46" ht="114" customHeight="1">
-      <c r="A46" s="83" t="inlineStr">
-        <is>
-          <t>Ensayo de desempeño</t>
-        </is>
-      </c>
-      <c r="B46" s="84" t="n"/>
-      <c r="C46" s="84" t="n"/>
-      <c r="D46" s="84" t="n"/>
-      <c r="E46" s="84" t="n"/>
-      <c r="F46" s="84" t="n"/>
-      <c r="G46" s="84" t="n"/>
-      <c r="H46" s="84" t="n"/>
-      <c r="I46" s="83" t="inlineStr">
-        <is>
-          <t>ASHRAE 70 (medición de rejillas)</t>
-        </is>
-      </c>
-      <c r="J46" s="84" t="n"/>
-      <c r="K46" s="84" t="n"/>
-      <c r="L46" s="84" t="n"/>
-      <c r="M46" s="84" t="n"/>
-      <c r="N46" s="84" t="n"/>
-      <c r="O46" s="84" t="n"/>
-    </row>
-    <row r="47" ht="38" customHeight="1"/>
-    <row r="48" ht="190" customHeight="1">
-      <c r="A48" s="85" t="inlineStr">
+    <row r="45" ht="50" customHeight="1"/>
+    <row r="46" ht="350" customHeight="1">
+      <c r="A46" s="85" t="inlineStr">
         <is>
           <t>3.1. La malla domina la pérdida del conjunto; el dimensionamiento por área neta combinada y la ΔP calculada por cierre de orificio (11 Pa) deben verificarse contra el área efectiva (Ak) del fabricante seleccionado (por confirmar con proveedor).</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="38" customHeight="1"/>
-    <row r="50" ht="76" customHeight="1">
-      <c r="A50" s="81" t="inlineStr">
+    <row r="47" ht="50" customHeight="1"/>
+    <row r="48" ht="100" customHeight="1">
+      <c r="A48" s="81" t="inlineStr">
         <is>
           <t>4. Candidatos comerciales</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="38" customHeight="1">
-      <c r="A51" s="86" t="inlineStr">
+    <row r="49" ht="100" customHeight="1">
+      <c r="A49" s="86" t="inlineStr">
         <is>
           <t>Tabla 3. Candidatos (consulta 2026-07-23).</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="76" customHeight="1">
-      <c r="A52" s="82" t="inlineStr">
+    <row r="50" ht="100" customHeight="1">
+      <c r="A50" s="82" t="inlineStr">
         <is>
           <t>Producto</t>
         </is>
       </c>
-      <c r="B52" s="82" t="n"/>
-      <c r="C52" s="82" t="n"/>
-      <c r="D52" s="82" t="inlineStr">
+      <c r="B50" s="82" t="n"/>
+      <c r="C50" s="82" t="n"/>
+      <c r="D50" s="82" t="inlineStr">
         <is>
           <t>Tipo / material</t>
         </is>
       </c>
-      <c r="E52" s="82" t="n"/>
-      <c r="F52" s="82" t="n"/>
-      <c r="G52" s="82" t="inlineStr">
+      <c r="E50" s="82" t="n"/>
+      <c r="F50" s="82" t="n"/>
+      <c r="G50" s="82" t="inlineStr">
         <is>
           <t>Pros</t>
         </is>
       </c>
-      <c r="H52" s="82" t="n"/>
-      <c r="I52" s="82" t="n"/>
-      <c r="J52" s="82" t="inlineStr">
+      <c r="H50" s="82" t="n"/>
+      <c r="I50" s="82" t="n"/>
+      <c r="J50" s="82" t="inlineStr">
         <is>
           <t>Contras</t>
         </is>
       </c>
-      <c r="K52" s="82" t="n"/>
-      <c r="L52" s="82" t="n"/>
-      <c r="M52" s="82" t="inlineStr">
+      <c r="K50" s="82" t="n"/>
+      <c r="L50" s="82" t="n"/>
+      <c r="M50" s="82" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="N52" s="82" t="n"/>
-      <c r="O52" s="82" t="n"/>
-    </row>
-    <row r="53" ht="266" customHeight="1">
+      <c r="N50" s="82" t="n"/>
+      <c r="O50" s="82" t="n"/>
+    </row>
+    <row r="51" ht="350" customHeight="1">
+      <c r="A51" s="83" t="inlineStr">
+        <is>
+          <t>Titus 50F / 50R</t>
+        </is>
+      </c>
+      <c r="B51" s="84" t="n"/>
+      <c r="C51" s="84" t="n"/>
+      <c r="D51" s="83" t="inlineStr">
+        <is>
+          <t>Eggcrate ½ in; aluminio, con versión íntegramente inox de fábrica</t>
+        </is>
+      </c>
+      <c r="E51" s="84" t="n"/>
+      <c r="F51" s="84" t="n"/>
+      <c r="G51" s="83" t="inlineStr">
+        <is>
+          <t>«Highest free area of any return grille»; única opción inox de catálogo</t>
+        </is>
+      </c>
+      <c r="H51" s="84" t="n"/>
+      <c r="I51" s="84" t="n"/>
+      <c r="J51" s="83" t="inlineStr">
+        <is>
+          <t>Importación; tamaño 353×336 por pedido</t>
+        </is>
+      </c>
+      <c r="K51" s="84" t="n"/>
+      <c r="L51" s="84" t="n"/>
+      <c r="M51" s="83" t="inlineStr">
+        <is>
+          <t>Titus 50F (PDF) (https://www.titus-hvac.com/file/1228/50F_50Rrprod_specialized_2017.pdf)</t>
+        </is>
+      </c>
+      <c r="N51" s="84" t="n"/>
+      <c r="O51" s="84" t="n"/>
+    </row>
+    <row r="52" ht="350" customHeight="1">
+      <c r="A52" s="83" t="inlineStr">
+        <is>
+          <t>Krueger EGC5</t>
+        </is>
+      </c>
+      <c r="B52" s="84" t="n"/>
+      <c r="C52" s="84" t="n"/>
+      <c r="D52" s="83" t="inlineStr">
+        <is>
+          <t>Eggcrate ½ in; aluminio</t>
+        </is>
+      </c>
+      <c r="E52" s="84" t="n"/>
+      <c r="F52" s="84" t="n"/>
+      <c r="G52" s="83" t="inlineStr">
+        <is>
+          <t>Amplia gama de tamaños (6×4 in a 96×96 in)</t>
+        </is>
+      </c>
+      <c r="H52" s="84" t="n"/>
+      <c r="I52" s="84" t="n"/>
+      <c r="J52" s="83" t="inlineStr">
+        <is>
+          <t>Sin ejecución inox</t>
+        </is>
+      </c>
+      <c r="K52" s="84" t="n"/>
+      <c r="L52" s="84" t="n"/>
+      <c r="M52" s="83" t="inlineStr">
+        <is>
+          <t>Krueger EGC5 (https://www.krueger-hvac.com/Catalog%20Home/Grilles/Grilles%20-%20Return/EGC5)</t>
+        </is>
+      </c>
+      <c r="N52" s="84" t="n"/>
+      <c r="O52" s="84" t="n"/>
+    </row>
+    <row r="53" ht="350" customHeight="1">
       <c r="A53" s="83" t="inlineStr">
         <is>
-          <t>Titus 50F / 50R</t>
+          <t>ProAire S.A.S (Bogotá)</t>
         </is>
       </c>
       <c r="B53" s="84" t="n"/>
       <c r="C53" s="84" t="n"/>
       <c r="D53" s="83" t="inlineStr">
         <is>
-          <t>Eggcrate ½ in; aluminio, con versión íntegramente inox de fábrica</t>
+          <t>Fabricación a medida con corte láser, inox 316</t>
         </is>
       </c>
       <c r="E53" s="84" t="n"/>
       <c r="F53" s="84" t="n"/>
       <c r="G53" s="83" t="inlineStr">
         <is>
-          <t>«Highest free area of any return grille»; única opción inox de catálogo</t>
+          <t>Medida exacta 353×336 y ejecución inox 316L local; vía recomendada</t>
         </is>
       </c>
       <c r="H53" s="84" t="n"/>
       <c r="I53" s="84" t="n"/>
       <c r="J53" s="83" t="inlineStr">
         <is>
-          <t>Importación; tamaño 353×336 por pedido</t>
+          <t>Submittal y Ak por confirmar con proveedor</t>
         </is>
       </c>
       <c r="K53" s="84" t="n"/>
       <c r="L53" s="84" t="n"/>
       <c r="M53" s="83" t="inlineStr">
         <is>
-          <t>Titus 50F (PDF) (https://www.titus-hvac.com/file/1228/50F_50Rrprod_specialized_2017.pdf)</t>
+          <t>proairecolombia.com (https://www.proairecolombia.com/productos/rejillas-y-difusores.html)</t>
         </is>
       </c>
       <c r="N53" s="84" t="n"/>
       <c r="O53" s="84" t="n"/>
     </row>
-    <row r="54" ht="266" customHeight="1">
+    <row r="54" ht="250" customHeight="1">
       <c r="A54" s="83" t="inlineStr">
         <is>
-          <t>Krueger EGC5</t>
+          <t>Laminaire (Colombia)</t>
         </is>
       </c>
       <c r="B54" s="84" t="n"/>
       <c r="C54" s="84" t="n"/>
       <c r="D54" s="83" t="inlineStr">
         <is>
-          <t>Eggcrate ½ in; aluminio</t>
+          <t>Rejillas y difusores en aluminio a pedido</t>
         </is>
       </c>
       <c r="E54" s="84" t="n"/>
       <c r="F54" s="84" t="n"/>
       <c r="G54" s="83" t="inlineStr">
         <is>
-          <t>Amplia gama de tamaños (6×4 in a 96×96 in)</t>
+          <t>Fabricación local con software de selección; marco para malla a pedido</t>
         </is>
       </c>
       <c r="H54" s="84" t="n"/>
       <c r="I54" s="84" t="n"/>
       <c r="J54" s="83" t="inlineStr">
         <is>
-          <t>Sin ejecución inox</t>
+          <t>Confirmar ejecución inox</t>
         </is>
       </c>
       <c r="K54" s="84" t="n"/>
       <c r="L54" s="84" t="n"/>
       <c r="M54" s="83" t="inlineStr">
         <is>
-          <t>Krueger EGC5 (https://www.krueger-hvac.com/Catalog%20Home/Grilles/Grilles%20-%20Return/EGC5)</t>
+          <t>laminaire.net (https://laminaire.net/)</t>
         </is>
       </c>
       <c r="N54" s="84" t="n"/>
       <c r="O54" s="84" t="n"/>
     </row>
-    <row r="55" ht="266" customHeight="1">
+    <row r="55" ht="150" customHeight="1">
       <c r="A55" s="83" t="inlineStr">
         <is>
-          <t>ProAire S.A.S (Bogotá)</t>
+          <t>CL Ingeniería (Bogotá)</t>
         </is>
       </c>
       <c r="B55" s="84" t="n"/>
       <c r="C55" s="84" t="n"/>
       <c r="D55" s="83" t="inlineStr">
         <is>
-          <t>Fabricación a medida con corte láser, inox 316</t>
+          <t>Rejillas y accesorios HVAC</t>
         </is>
       </c>
       <c r="E55" s="84" t="n"/>
       <c r="F55" s="84" t="n"/>
       <c r="G55" s="83" t="inlineStr">
         <is>
-          <t>Medida exacta 353×336 y ejecución inox 316L local; vía recomendada</t>
+          <t>Canal local adicional</t>
         </is>
       </c>
       <c r="H55" s="84" t="n"/>
       <c r="I55" s="84" t="n"/>
       <c r="J55" s="83" t="inlineStr">
         <is>
-          <t>Submittal y Ak por confirmar con proveedor</t>
+          <t>Catálogo genérico</t>
         </is>
       </c>
       <c r="K55" s="84" t="n"/>
       <c r="L55" s="84" t="n"/>
       <c r="M55" s="83" t="inlineStr">
         <is>
-          <t>proairecolombia.com (https://www.proairecolombia.com/productos/rejillas-y-difusores.html)</t>
+          <t>clingenieria.co (https://clingenieria.co/)</t>
         </is>
       </c>
       <c r="N55" s="84" t="n"/>
       <c r="O55" s="84" t="n"/>
     </row>
-    <row r="56" ht="190" customHeight="1">
-      <c r="A56" s="83" t="inlineStr">
-        <is>
-          <t>Laminaire (Colombia)</t>
-        </is>
-      </c>
-      <c r="B56" s="84" t="n"/>
-      <c r="C56" s="84" t="n"/>
-      <c r="D56" s="83" t="inlineStr">
-        <is>
-          <t>Rejillas y difusores en aluminio a pedido</t>
-        </is>
-      </c>
-      <c r="E56" s="84" t="n"/>
-      <c r="F56" s="84" t="n"/>
-      <c r="G56" s="83" t="inlineStr">
-        <is>
-          <t>Fabricación local con software de selección; marco para malla a pedido</t>
-        </is>
-      </c>
-      <c r="H56" s="84" t="n"/>
-      <c r="I56" s="84" t="n"/>
-      <c r="J56" s="83" t="inlineStr">
-        <is>
-          <t>Confirmar ejecución inox</t>
-        </is>
-      </c>
-      <c r="K56" s="84" t="n"/>
-      <c r="L56" s="84" t="n"/>
-      <c r="M56" s="83" t="inlineStr">
-        <is>
-          <t>laminaire.net (https://laminaire.net/)</t>
-        </is>
-      </c>
-      <c r="N56" s="84" t="n"/>
-      <c r="O56" s="84" t="n"/>
-    </row>
-    <row r="57" ht="114" customHeight="1">
-      <c r="A57" s="83" t="inlineStr">
-        <is>
-          <t>CL Ingeniería (Bogotá)</t>
-        </is>
-      </c>
-      <c r="B57" s="84" t="n"/>
-      <c r="C57" s="84" t="n"/>
-      <c r="D57" s="83" t="inlineStr">
-        <is>
-          <t>Rejillas y accesorios HVAC</t>
-        </is>
-      </c>
-      <c r="E57" s="84" t="n"/>
-      <c r="F57" s="84" t="n"/>
-      <c r="G57" s="83" t="inlineStr">
-        <is>
-          <t>Canal local adicional</t>
-        </is>
-      </c>
-      <c r="H57" s="84" t="n"/>
-      <c r="I57" s="84" t="n"/>
-      <c r="J57" s="83" t="inlineStr">
-        <is>
-          <t>Catálogo genérico</t>
-        </is>
-      </c>
-      <c r="K57" s="84" t="n"/>
-      <c r="L57" s="84" t="n"/>
-      <c r="M57" s="83" t="inlineStr">
-        <is>
-          <t>clingenieria.co (https://clingenieria.co/)</t>
-        </is>
-      </c>
-      <c r="N57" s="84" t="n"/>
-      <c r="O57" s="84" t="n"/>
-    </row>
-    <row r="58" ht="38" customHeight="1"/>
-    <row r="59" ht="38" customHeight="1">
-      <c r="A59" s="81" t="inlineStr">
+    <row r="56" ht="50" customHeight="1"/>
+    <row r="57" ht="50" customHeight="1">
+      <c r="A57" s="81" t="inlineStr">
         <is>
           <t>5. Instalación</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="456" customHeight="1">
+    <row r="58" ht="450" customHeight="1">
+      <c r="A58" s="85" t="inlineStr">
+        <is>
+          <t>5.1. Montaje a ras de muro exterior con marco perimetral sellado con silicona RTV neutra (compatible con hipoclorito; Chemical Resistance of RTV Silicone Sealants (PDF) (https://irp.cdn-website.com/63168859/files/uploaded/Chemical%20Resistance%20of%20RTV%20Silicone%20Sealants%20Chart.pdf), consulta 2026-07-23) y ferretería inox 316 (A4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="150" customHeight="1">
+      <c r="A59" s="85" t="inlineStr">
+        <is>
+          <t>5.2. Las bocas exteriores se orientan preferentemente a sotavento respecto de las fuentes de cloro de la planta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="150" customHeight="1">
       <c r="A60" s="85" t="inlineStr">
         <is>
-          <t>5.1. Montaje a ras de muro exterior con marco perimetral sellado con silicona RTV neutra (compatible con hipoclorito; Chemical Resistance of RTV Silicone Sealants (PDF) (https://irp.cdn-website.com/63168859/files/uploaded/Chemical%20Resistance%20of%20RTV%20Silicone%20Sealants%20Chart.pdf), consulta 2026-07-23) y ferretería inox 316 (A4).</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="38" customHeight="1"/>
-    <row r="62" ht="114" customHeight="1">
-      <c r="A62" s="85" t="inlineStr">
-        <is>
-          <t>5.2. Las bocas exteriores se orientan preferentemente a sotavento respecto de las fuentes de cloro de la planta.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="114" customHeight="1">
+          <t>5.3. Programa de limpieza de la malla según carga de polvo observada en comisionamiento (dato típico de operación).</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="50" customHeight="1"/>
+    <row r="62" ht="100" customHeight="1">
+      <c r="A62" s="81" t="inlineStr">
+        <is>
+          <t>6. Normas aplicables</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="500" customHeight="1">
       <c r="A63" s="85" t="inlineStr">
         <is>
-          <t>5.3. Programa de limpieza de la malla según carga de polvo observada en comisionamiento (dato típico de operación).</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="38" customHeight="1"/>
-    <row r="65" ht="76" customHeight="1">
-      <c r="A65" s="81" t="inlineStr">
-        <is>
-          <t>6. Normas aplicables</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="494" customHeight="1">
-      <c r="A66" s="85" t="inlineStr">
-        <is>
           <t>6.1. ASHRAE 70 (método de ensayo y reporte de desempeño de rejillas); correlación de área libre para transferencia de aire según Building Science BA-0006 (https://buildingscience.com/sites/default/files/migrate/pdf/BA-0006_Discuss_transfer_grilles.pdf) (consulta 2026-07-23); ISO 12944 / NACE-AMPP para la selección de materiales en el ambiente clorado.</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="38" customHeight="1"/>
   </sheetData>
-  <mergeCells count="100">
+  <mergeCells count="96">
     <mergeCell ref="I44:O44"/>
     <mergeCell ref="D53:F53"/>
-    <mergeCell ref="A50:O50"/>
-    <mergeCell ref="A57:C57"/>
     <mergeCell ref="N3:O3"/>
     <mergeCell ref="A25:H25"/>
-    <mergeCell ref="I30:O30"/>
+    <mergeCell ref="J50:L50"/>
     <mergeCell ref="N5:O5"/>
-    <mergeCell ref="I46:O46"/>
     <mergeCell ref="C2:L3"/>
     <mergeCell ref="A52:C52"/>
+    <mergeCell ref="G50:I50"/>
     <mergeCell ref="J52:L52"/>
     <mergeCell ref="M53:O53"/>
     <mergeCell ref="G52:I52"/>
@@ -4952,75 +4938,73 @@
     <mergeCell ref="A44:H44"/>
     <mergeCell ref="I24:O24"/>
     <mergeCell ref="B1:B5"/>
-    <mergeCell ref="D57:F57"/>
     <mergeCell ref="A40:H40"/>
     <mergeCell ref="A15:H15"/>
     <mergeCell ref="A24:H24"/>
+    <mergeCell ref="I35:O35"/>
     <mergeCell ref="A55:C55"/>
     <mergeCell ref="I10:O10"/>
     <mergeCell ref="N2:O2"/>
     <mergeCell ref="G55:I55"/>
-    <mergeCell ref="M57:O57"/>
     <mergeCell ref="A27:H27"/>
+    <mergeCell ref="G51:I51"/>
+    <mergeCell ref="A62:O62"/>
     <mergeCell ref="D55:F55"/>
     <mergeCell ref="I11:O11"/>
-    <mergeCell ref="I45:O45"/>
     <mergeCell ref="G54:I54"/>
+    <mergeCell ref="A20:O20"/>
     <mergeCell ref="D54:F54"/>
     <mergeCell ref="A42:H42"/>
-    <mergeCell ref="M56:O56"/>
-    <mergeCell ref="G56:I56"/>
+    <mergeCell ref="A48:O48"/>
+    <mergeCell ref="A22:H22"/>
     <mergeCell ref="I28:O28"/>
-    <mergeCell ref="A59:O59"/>
+    <mergeCell ref="A51:C51"/>
     <mergeCell ref="I37:O37"/>
     <mergeCell ref="N6:O6"/>
     <mergeCell ref="A28:H28"/>
     <mergeCell ref="N4:O4"/>
     <mergeCell ref="J53:L53"/>
     <mergeCell ref="I23:O23"/>
-    <mergeCell ref="A30:H30"/>
     <mergeCell ref="G53:I53"/>
     <mergeCell ref="J55:L55"/>
+    <mergeCell ref="A50:C50"/>
     <mergeCell ref="J54:L54"/>
+    <mergeCell ref="A33:O33"/>
     <mergeCell ref="A41:H41"/>
-    <mergeCell ref="J56:L56"/>
     <mergeCell ref="A17:O17"/>
-    <mergeCell ref="A60:O61"/>
+    <mergeCell ref="D51:F51"/>
     <mergeCell ref="I27:O27"/>
-    <mergeCell ref="A35:O35"/>
     <mergeCell ref="A26:H26"/>
-    <mergeCell ref="A66:O67"/>
+    <mergeCell ref="I36:O36"/>
+    <mergeCell ref="D50:F50"/>
     <mergeCell ref="A1:A5"/>
     <mergeCell ref="A9:O9"/>
     <mergeCell ref="C1:L1"/>
-    <mergeCell ref="J57:L57"/>
-    <mergeCell ref="A18:O19"/>
+    <mergeCell ref="I22:O22"/>
+    <mergeCell ref="A35:H35"/>
     <mergeCell ref="A10:H10"/>
     <mergeCell ref="I12:O12"/>
-    <mergeCell ref="A32:O33"/>
+    <mergeCell ref="M51:O51"/>
     <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A65:O65"/>
     <mergeCell ref="A39:H39"/>
     <mergeCell ref="I14:O14"/>
     <mergeCell ref="I39:O39"/>
     <mergeCell ref="M54:O54"/>
-    <mergeCell ref="G57:I57"/>
-    <mergeCell ref="A56:C56"/>
     <mergeCell ref="I29:O29"/>
+    <mergeCell ref="A36:H36"/>
     <mergeCell ref="A11:H11"/>
     <mergeCell ref="I38:O38"/>
-    <mergeCell ref="A45:H45"/>
-    <mergeCell ref="A21:O21"/>
     <mergeCell ref="I13:O13"/>
+    <mergeCell ref="A57:O57"/>
     <mergeCell ref="I40:O40"/>
-    <mergeCell ref="D56:F56"/>
     <mergeCell ref="I15:O15"/>
     <mergeCell ref="A53:C53"/>
     <mergeCell ref="A37:H37"/>
-    <mergeCell ref="A46:H46"/>
     <mergeCell ref="N1:O1"/>
     <mergeCell ref="A12:H12"/>
+    <mergeCell ref="J51:L51"/>
     <mergeCell ref="I26:O26"/>
+    <mergeCell ref="M50:O50"/>
     <mergeCell ref="A14:H14"/>
     <mergeCell ref="A23:H23"/>
     <mergeCell ref="I25:O25"/>
